--- a/workbooks/start-of-demographic-transition-ru.xlsx
+++ b/workbooks/start-of-demographic-transition-ru.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7011787-ECD5-4490-B243-A45CD6C74705}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA0EC1D-23CB-4152-9187-578CA06D1CF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1515" windowWidth="23985" windowHeight="21000" activeTab="4" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="5" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="5" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="NR" sheetId="2" r:id="rId3"/>
     <sheet name="MR" sheetId="3" r:id="rId4"/>
     <sheet name="BR" sheetId="4" r:id="rId5"/>
+    <sheet name="все вместе" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="STEP">NR!$V$5</definedName>
@@ -25,7 +26,7 @@
     <definedName name="STEP_NR">NR!$V$5</definedName>
     <definedName name="STEP_RSFSR">RSFSR!$V$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,12 +34,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -68,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
   <si>
     <t>год</t>
   </si>
@@ -121,12 +117,6 @@
     <t>Малороссия: сдвиг почти нулевой, около +0.1 года</t>
   </si>
   <si>
-    <t>Белоруссия: около &lt;b&gt;+0.6 года</t>
-  </si>
-  <si>
-    <t>Новороссия: около &lt;b&gt;-0.3 года</t>
-  </si>
-  <si>
     <t>Для РСФСР исключение аномальных лет сдвигает пересечение 10%-го уровня заметнее — примерно с 1921.5 к 1918.4.</t>
   </si>
   <si>
@@ -140,9 +130,6 @@
   </si>
   <si>
     <t xml:space="preserve">в Малороссии (ок. 1905–1906) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">и Белоруссии (ок. 1907), </t>
   </si>
   <si>
     <t xml:space="preserve">тогда как в Новороссии оно относится лишь к 1917 г., </t>
@@ -171,6 +158,18 @@
   <si>
     <t>Для РСФСР и Новороссии до 1914 года 10%-го снижения рождаемости ещё не происходит, и для них момент начала перехода определяется по тренду.</t>
   </si>
+  <si>
+    <t>Белоруссия: около +0.6 года</t>
+  </si>
+  <si>
+    <t>Новороссия: около -0.3 года</t>
+  </si>
+  <si>
+    <t xml:space="preserve">и Белоруссии (ок. 1907-1908), </t>
+  </si>
+  <si>
+    <t>РСФСР-1991</t>
+  </si>
 </sst>
 </file>
 
@@ -179,7 +178,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +200,13 @@
       <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -230,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -252,6 +258,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +433,7 @@
                   <c:v>50.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>52.1</c:v>
@@ -432,22 +442,22 @@
                   <c:v>51.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>52.5</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>52.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>52.4</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.6</c:v>
+                  <c:v>48.7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>49.8</c:v>
@@ -843,7 +853,7 @@
                   <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>52.1</c:v>
@@ -852,19 +862,19 @@
                   <c:v>51.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>52.5</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>52.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>52.4</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.3</c:v>
+                  <c:v>51.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>50.7</c:v>
@@ -2114,6 +2124,7 @@
         <c:axId val="445041824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="38"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2484,6 +2495,7 @@
         <c:axId val="976203568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="38"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2870,6 +2882,8 @@
         <c:axId val="445036544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="50"/>
+          <c:min val="40"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3340,6 +3354,972 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>РСФСР-1991</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$B$4:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>51.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>51.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>49.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>50.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48.7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Новороссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$C$4:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>52.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>50.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>48.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>47.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Малороссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$D$4:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>38.799999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Белоруссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$E$4:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="733148016"/>
+        <c:axId val="733147688"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="733148016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1914"/>
+          <c:min val="1896"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="733147688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="733147688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="38"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="733148016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -3663,6 +4643,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -7276,6 +8296,522 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8099,6 +9635,228 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5ED5177-F0B8-42BA-BD18-16A1DB2A10F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.79607</cdr:x>
+      <cdr:y>0.46007</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.9012</cdr:x>
+      <cdr:y>0.5118</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39AD6A7D-36C1-43D2-A5DC-C975E3E33650}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5986462" y="4829175"/>
+          <a:ext cx="790575" cy="542925"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Новороссия</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.76314</cdr:x>
+      <cdr:y>0.65789</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.8708</cdr:x>
+      <cdr:y>0.72414</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1661F072-E2A9-4D7D-A4C3-B3902A938AEB}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5738812" y="6905624"/>
+          <a:ext cx="809625" cy="695325"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Белоруссия</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.71881</cdr:x>
+      <cdr:y>0.85935</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.83281</cdr:x>
+      <cdr:y>0.89837</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65B1D80D-A1E1-4282-9A2F-5C1A4C981F94}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5405438" y="9020175"/>
+          <a:ext cx="857250" cy="409574"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Малороссия</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.76821</cdr:x>
+      <cdr:y>0.13612</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.886</cdr:x>
+      <cdr:y>0.20327</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23DB286-897B-45DB-9D53-5D23C60153B0}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5776912" y="1428750"/>
+          <a:ext cx="885825" cy="704850"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1"/>
+            <a:t>РСФСР-1991</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8431,22 +10189,22 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -8471,62 +10229,62 @@
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="B26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="B31" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="B32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8574,7 +10332,7 @@
         <v>5</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -8586,11 +10344,11 @@
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C22">TREND($B$4:$B$22,$A$4:$A$22,A4:A22)</f>
-        <v>52.765263157894708</v>
+        <v>52.816315789473663</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.20666666666664923</v>
+        <v>0.20824561403509279</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -8605,7 +10363,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="6">
-        <v>52.558596491228059</v>
+        <v>52.60807017543857</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -8617,11 +10375,11 @@
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.39167182024321789</v>
+        <v>0.39428273426939597</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.39167182024320368</v>
+        <v>0.39428273426928229</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -8633,7 +10391,7 @@
         <v>50.7</v>
       </c>
       <c r="C6" s="6">
-        <v>52.35192982456141</v>
+        <v>52.399824561403534</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -8645,7 +10403,7 @@
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U22" si="2">100 - 100 * C6/$C$4</f>
-        <v>0.78334364048642158</v>
+        <v>0.78856546853867826</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -8654,10 +10412,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="C7" s="6">
-        <v>52.14526315789476</v>
+        <v>52.191578947368441</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -8665,11 +10423,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T22" si="3">100 - 100 * B7/$B$4</f>
-        <v>3.2075471698113205</v>
+        <v>3.0188679245283083</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>1.1750154607296537</v>
+        <v>1.18284820280806</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -8681,7 +10439,7 @@
         <v>52.1</v>
       </c>
       <c r="C8" s="6">
-        <v>51.938596491228054</v>
+        <v>51.983333333333348</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -8693,7 +10451,7 @@
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>1.5666872809729711</v>
+        <v>1.577130937077456</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -8705,7 +10463,7 @@
         <v>51.7</v>
       </c>
       <c r="C9" s="6">
-        <v>51.731929824561405</v>
+        <v>51.775087719298256</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -8717,7 +10475,7 @@
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>1.9583591012161889</v>
+        <v>1.971413671346852</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -8726,10 +10484,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="C10" s="6">
-        <v>51.525263157894756</v>
+        <v>51.566842105263163</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -8737,11 +10495,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>0.94339622641508925</v>
+        <v>0.75471698113207708</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>2.3500309214594068</v>
+        <v>2.3656964056162337</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -8750,10 +10508,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="C11" s="6">
-        <v>51.31859649122805</v>
+        <v>51.35859649122807</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -8761,11 +10519,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>1.6981132075471663</v>
+        <v>1.5094339622641542</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>2.7417027417027242</v>
+        <v>2.7599791398856297</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -8774,10 +10532,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="C12" s="6">
-        <v>51.1119298245614</v>
+        <v>51.150350877192977</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -8785,11 +10543,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>1.1320754716981156</v>
+        <v>0.94339622641508925</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>3.1333745619459421</v>
+        <v>3.1542618741550257</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -8798,10 +10556,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="C13" s="6">
-        <v>50.905263157894751</v>
+        <v>50.942105263157885</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -8809,11 +10567,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>8.3018867924528337</v>
+        <v>8.1132075471698073</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>3.52504638218916</v>
+        <v>3.5485446084244217</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -8822,10 +10580,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="C14" s="6">
-        <v>50.698596491228045</v>
+        <v>50.733859649122792</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -8833,11 +10591,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>3.2075471698113205</v>
+        <v>3.0188679245283083</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>3.9167182024324774</v>
+        <v>3.9428273426938034</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -8846,10 +10604,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="C15" s="6">
-        <v>50.491929824561396</v>
+        <v>50.525614035087699</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -8857,11 +10615,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="3"/>
-        <v>3.2075471698113205</v>
+        <v>3.0188679245283083</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>4.3083900226757095</v>
+        <v>4.3371100769631852</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -8873,7 +10631,7 @@
         <v>49.8</v>
       </c>
       <c r="C16" s="6">
-        <v>50.285263157894747</v>
+        <v>50.317368421052606</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -8885,7 +10643,7 @@
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>4.7000618429189132</v>
+        <v>4.7313928112325812</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -8897,7 +10655,7 @@
         <v>50.1</v>
       </c>
       <c r="C17" s="6">
-        <v>50.078596491228041</v>
+        <v>50.10912280701757</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -8909,7 +10667,7 @@
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>5.0917336631622447</v>
+        <v>5.1256755455018634</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -8921,7 +10679,7 @@
         <v>51</v>
       </c>
       <c r="C18" s="6">
-        <v>49.871929824561391</v>
+        <v>49.900877192982477</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -8933,7 +10691,7 @@
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>5.4834054834054484</v>
+        <v>5.5199582797712594</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -8945,7 +10703,7 @@
         <v>50.7</v>
       </c>
       <c r="C19" s="6">
-        <v>49.665263157894742</v>
+        <v>49.692631578947385</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -8957,7 +10715,7 @@
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>5.8750773036486663</v>
+        <v>5.9142410140406412</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -8969,7 +10727,7 @@
         <v>48.7</v>
       </c>
       <c r="C20" s="6">
-        <v>49.458596491228093</v>
+        <v>49.484385964912292</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -8981,7 +10739,7 @@
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>6.2667491238918842</v>
+        <v>6.3085237483100371</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -8993,7 +10751,7 @@
         <v>48.6</v>
       </c>
       <c r="C21" s="6">
-        <v>49.251929824561387</v>
+        <v>49.276140350877199</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -9005,7 +10763,7 @@
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>6.6584209441352158</v>
+        <v>6.7028064825794331</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -9016,7 +10774,7 @@
         <v>48.3</v>
       </c>
       <c r="C22" s="6">
-        <v>49.045263157894738</v>
+        <v>49.067894736842106</v>
       </c>
       <c r="S22" s="4">
         <v>1914</v>
@@ -9027,7 +10785,7 @@
       </c>
       <c r="U22" s="6">
         <f t="shared" si="2"/>
-        <v>7.0500927643784337</v>
+        <v>7.0970892168488149</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -9037,7 +10795,7 @@
       </c>
       <c r="C23" s="6">
         <f>C22-$D$4</f>
-        <v>48.838596491228088</v>
+        <v>48.859649122807014</v>
       </c>
       <c r="S23" s="4">
         <f>S22+1</f>
@@ -9045,7 +10803,7 @@
       </c>
       <c r="U23" s="6">
         <f t="shared" ref="U23:U35" si="5">U22+STEP</f>
-        <v>7.5276294340546883</v>
+        <v>7.5746258865250695</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -9055,7 +10813,7 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" ref="C24:C29" si="6">C23-$D$4</f>
-        <v>48.631929824561439</v>
+        <v>48.651403508771921</v>
       </c>
       <c r="S24" s="4">
         <f t="shared" ref="S24:S35" si="7">S23+1</f>
@@ -9063,7 +10821,7 @@
       </c>
       <c r="U24" s="6">
         <f t="shared" si="5"/>
-        <v>8.005166103730943</v>
+        <v>8.0521625562013242</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -9073,7 +10831,7 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="6"/>
-        <v>48.42526315789479</v>
+        <v>48.443157894736828</v>
       </c>
       <c r="S25" s="4">
         <f t="shared" si="7"/>
@@ -9081,7 +10839,7 @@
       </c>
       <c r="U25" s="6">
         <f t="shared" si="5"/>
-        <v>8.4827027734071976</v>
+        <v>8.5296992258775788</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -9091,7 +10849,7 @@
       </c>
       <c r="C26" s="6">
         <f t="shared" si="6"/>
-        <v>48.218596491228141</v>
+        <v>48.234912280701735</v>
       </c>
       <c r="S26" s="4">
         <f t="shared" si="7"/>
@@ -9099,7 +10857,7 @@
       </c>
       <c r="U26" s="6">
         <f t="shared" si="5"/>
-        <v>8.9602394430834522</v>
+        <v>9.0072358955538334</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -9109,7 +10867,7 @@
       </c>
       <c r="C27" s="6">
         <f t="shared" si="6"/>
-        <v>48.011929824561491</v>
+        <v>48.026666666666642</v>
       </c>
       <c r="S27" s="4">
         <f t="shared" si="7"/>
@@ -9117,7 +10875,7 @@
       </c>
       <c r="U27" s="6">
         <f t="shared" si="5"/>
-        <v>9.4377761127597068</v>
+        <v>9.484772565230088</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -9127,15 +10885,15 @@
       </c>
       <c r="C28" s="6">
         <f t="shared" si="6"/>
-        <v>47.805263157894842</v>
+        <v>47.81842105263155</v>
       </c>
       <c r="S28" s="4">
         <f t="shared" si="7"/>
         <v>1920</v>
       </c>
-      <c r="U28" s="6">
+      <c r="U28" s="12">
         <f t="shared" si="5"/>
-        <v>9.9153127824359615</v>
+        <v>9.9623092349063427</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -9145,7 +10903,7 @@
       </c>
       <c r="C29" s="6">
         <f t="shared" si="6"/>
-        <v>47.598596491228193</v>
+        <v>47.610175438596457</v>
       </c>
       <c r="S29" s="7">
         <f t="shared" si="7"/>
@@ -9154,7 +10912,7 @@
       <c r="T29" s="9"/>
       <c r="U29" s="12">
         <f t="shared" si="5"/>
-        <v>10.392849452112216</v>
+        <v>10.439845904582597</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -9164,7 +10922,7 @@
       </c>
       <c r="U30" s="6">
         <f t="shared" si="5"/>
-        <v>10.870386121788471</v>
+        <v>10.917382574258852</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -9174,7 +10932,7 @@
       </c>
       <c r="U31" s="6">
         <f t="shared" si="5"/>
-        <v>11.347922791464725</v>
+        <v>11.394919243935107</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -9184,7 +10942,7 @@
       </c>
       <c r="U32" s="6">
         <f t="shared" si="5"/>
-        <v>11.82545946114098</v>
+        <v>11.872455913611361</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -9194,7 +10952,7 @@
       </c>
       <c r="U33" s="6">
         <f t="shared" si="5"/>
-        <v>12.302996130817235</v>
+        <v>12.349992583287616</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -9204,7 +10962,7 @@
       </c>
       <c r="U34" s="6">
         <f t="shared" si="5"/>
-        <v>12.780532800493489</v>
+        <v>12.82752925296387</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -9214,7 +10972,7 @@
       </c>
       <c r="U35" s="6">
         <f t="shared" si="5"/>
-        <v>13.258069470169744</v>
+        <v>13.305065922640125</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15">
@@ -9260,7 +11018,7 @@
         <v>1899</v>
       </c>
       <c r="B45" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -9287,7 +11045,7 @@
         <v>1902</v>
       </c>
       <c r="B48" s="5">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9296,7 +11054,7 @@
         <v>1903</v>
       </c>
       <c r="B49" s="5">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9305,7 +11063,7 @@
         <v>1904</v>
       </c>
       <c r="B50" s="5">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9321,7 +11079,7 @@
         <v>1906</v>
       </c>
       <c r="B52" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9330,7 +11088,7 @@
         <v>1907</v>
       </c>
       <c r="B53" s="5">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9435,7 +11193,7 @@
         <v>5</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -10160,7 +11918,7 @@
         <v>5</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -10801,7 +12559,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10845,7 +12604,7 @@
         <v>5</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -11482,6 +13241,372 @@
       </c>
       <c r="B49" s="5">
         <v>40.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03EEFA1-9E72-4B80-AF4D-F111553A5002}">
+  <dimension ref="A3:E22"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" ht="15">
+      <c r="A3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4">
+        <v>1896</v>
+      </c>
+      <c r="B4" s="5">
+        <v>53</v>
+      </c>
+      <c r="C4" s="5">
+        <v>52.1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>48.9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4">
+        <f>A4+1</f>
+        <v>1897</v>
+      </c>
+      <c r="B5" s="5">
+        <v>53</v>
+      </c>
+      <c r="C5" s="5">
+        <v>51.5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>48.4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4">
+        <f t="shared" ref="A6:A21" si="0">A5+1</f>
+        <v>1898</v>
+      </c>
+      <c r="B6" s="5">
+        <v>50.7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>50.4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46.2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4">
+        <f t="shared" si="0"/>
+        <v>1899</v>
+      </c>
+      <c r="B7" s="5">
+        <v>51.4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>51.2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>47.6</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="B8" s="5">
+        <v>52.1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>50.4</v>
+      </c>
+      <c r="D8" s="5">
+        <v>47.9</v>
+      </c>
+      <c r="E8" s="5">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>1901</v>
+      </c>
+      <c r="B9" s="5">
+        <v>51.7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>1902</v>
+      </c>
+      <c r="B10" s="5">
+        <v>52.6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>50.4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46</v>
+      </c>
+      <c r="E10" s="5">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>1903</v>
+      </c>
+      <c r="B11" s="5">
+        <v>52.2</v>
+      </c>
+      <c r="C11" s="5">
+        <v>50.1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>44.9</v>
+      </c>
+      <c r="E11" s="5">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>1904</v>
+      </c>
+      <c r="B12" s="5">
+        <v>52.5</v>
+      </c>
+      <c r="C12" s="5">
+        <v>50.1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>44.2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>1905</v>
+      </c>
+      <c r="B13" s="5">
+        <v>48.7</v>
+      </c>
+      <c r="C13" s="5">
+        <v>45.9</v>
+      </c>
+      <c r="D13" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>1906</v>
+      </c>
+      <c r="B14" s="5">
+        <v>51.4</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46.9</v>
+      </c>
+      <c r="D14" s="5">
+        <v>43.3</v>
+      </c>
+      <c r="E14" s="5">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>1907</v>
+      </c>
+      <c r="B15" s="5">
+        <v>51.4</v>
+      </c>
+      <c r="C15" s="5">
+        <v>50.2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>44.6</v>
+      </c>
+      <c r="E15" s="5">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="B16" s="5">
+        <v>49.8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>47.6</v>
+      </c>
+      <c r="D16" s="5">
+        <v>42.2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>1909</v>
+      </c>
+      <c r="B17" s="5">
+        <v>50.1</v>
+      </c>
+      <c r="C17" s="5">
+        <v>48.8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>41.2</v>
+      </c>
+      <c r="E17" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="B18" s="5">
+        <v>51</v>
+      </c>
+      <c r="C18" s="5">
+        <v>48</v>
+      </c>
+      <c r="D18" s="5">
+        <v>40.9</v>
+      </c>
+      <c r="E18" s="5">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="B19" s="5">
+        <v>50.7</v>
+      </c>
+      <c r="C19" s="5">
+        <v>48.2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="E19" s="5">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>1912</v>
+      </c>
+      <c r="B20" s="5">
+        <v>48.7</v>
+      </c>
+      <c r="C20" s="5">
+        <v>47.9</v>
+      </c>
+      <c r="D20" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="E20" s="5">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>1913</v>
+      </c>
+      <c r="B21" s="5">
+        <v>48.6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E21" s="5">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4">
+        <v>1914</v>
+      </c>
+      <c r="B22" s="5">
+        <v>48.3</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/start-of-demographic-transition-ru.xlsx
+++ b/workbooks/start-of-demographic-transition-ru.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA0EC1D-23CB-4152-9187-578CA06D1CF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D2F907-E687-4AA9-A975-E42F02DEE101}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="5" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="6" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="NR" sheetId="2" r:id="rId3"/>
     <sheet name="MR" sheetId="3" r:id="rId4"/>
     <sheet name="BR" sheetId="4" r:id="rId5"/>
-    <sheet name="все вместе" sheetId="6" r:id="rId6"/>
+    <sheet name="BR без Смоленской" sheetId="7" r:id="rId6"/>
+    <sheet name="все вместе" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="STEP">NR!$V$5</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
   <si>
     <t>год</t>
   </si>
@@ -170,6 +171,16 @@
   <si>
     <t>РСФСР-1991</t>
   </si>
+  <si>
+    <t>Белоруссия
+без Смоленской</t>
+  </si>
+  <si>
+    <t>Белоруссия без Смоленской губернии</t>
+  </si>
+  <si>
+    <t>Белоруссия со Смоленской губернией</t>
+  </si>
 </sst>
 </file>
 
@@ -236,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -258,9 +269,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,61 +440,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>53</c:v>
+                  <c:v>53.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53</c:v>
+                  <c:v>53.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.7</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.4</c:v>
+                  <c:v>51.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52.1</c:v>
+                  <c:v>52.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51.7</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52.6</c:v>
+                  <c:v>52.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.2</c:v>
+                  <c:v>52.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.5</c:v>
+                  <c:v>52.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.7</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.4</c:v>
+                  <c:v>51.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.4</c:v>
+                  <c:v>51.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>49.8</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>50.1</c:v>
+                  <c:v>50.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>51</c:v>
+                  <c:v>51.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.7</c:v>
+                  <c:v>50.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.7</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.6</c:v>
+                  <c:v>48.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48.3</c:v>
+                  <c:v>48.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -672,6 +688,1523 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BR!$B$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>рождаемость</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BR!$A$32:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BR!$B$32:$B$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-69DC-4EE2-AC40-5AAF78F84760}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="976159888"/>
+        <c:axId val="976160368"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="976159888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="976160368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="976160368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="976159888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>РСФСР-1991</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$B$4:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>53.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>52.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>51.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>51.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>50.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>51.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48.8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Новороссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$C$4:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>52.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>50.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>48.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>47.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Малороссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$D$4:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>38.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'все вместе'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Белоруссия</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$E$4:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>45.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6912-4F2C-AF86-A269FE454EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Белоруссия без Смоленской</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'все вместе'!$A$4:$A$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1913</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'все вместе'!$F$4:$F$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>45.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>42.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-D9BE-48B1-BE13-19ADDB13A2C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="733148016"/>
+        <c:axId val="733147688"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="733148016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1914"/>
+          <c:min val="1896"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="733147688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="733147688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="54"/>
+          <c:min val="38"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="733148016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -847,46 +2380,46 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>53</c:v>
+                  <c:v>53.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53</c:v>
+                  <c:v>53.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.4</c:v>
+                  <c:v>51.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52.1</c:v>
+                  <c:v>52.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51.7</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52.6</c:v>
+                  <c:v>52.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.2</c:v>
+                  <c:v>52.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.5</c:v>
+                  <c:v>52.7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.4</c:v>
+                  <c:v>51.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.4</c:v>
+                  <c:v>51.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.7</c:v>
+                  <c:v>50.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.7</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.6</c:v>
+                  <c:v>48.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48.3</c:v>
+                  <c:v>48.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1152,10 +2685,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>NR!$A$4:$A$21</c:f>
+              <c:f>NR!$A$4:$A$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1896</c:v>
                 </c:pt>
@@ -1209,16 +2742,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>NR!$B$4:$B$21</c:f>
+              <c:f>NR!$B$4:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>52.1</c:v>
                 </c:pt>
@@ -1272,6 +2808,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1298,6 +2837,7 @@
         <c:axId val="445036544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1914"/>
           <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1538,10 +3078,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>NR!$A$32:$A$49</c:f>
+              <c:f>NR!$A$32:$A$50</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1896</c:v>
                 </c:pt>
@@ -1595,16 +3135,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1914</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>NR!$B$32:$B$49</c:f>
+              <c:f>NR!$B$32:$B$50</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>52.1</c:v>
                 </c:pt>
@@ -1643,6 +3186,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46.5</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="General">
+                  <c:v>44.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1669,6 +3215,7 @@
         <c:axId val="976153648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1914"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2034,7 +3581,7 @@
                   <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.799999999999997</c:v>
+                  <c:v>38.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2406,7 +3953,7 @@
                   <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.799999999999997</c:v>
+                  <c:v>38.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3382,11 +4929,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'все вместе'!$B$3</c:f>
+              <c:f>'BR без Смоленской'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>РСФСР-1991</c:v>
+                  <c:v>рождаемость</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3394,7 +4941,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3405,11 +4952,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -3419,7 +4966,7 @@
             <c:spPr>
               <a:ln w="19050" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
                 <a:prstDash val="sysDot"/>
               </a:ln>
@@ -3431,10 +4978,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'все вместе'!$A$4:$A$22</c:f>
+              <c:f>'BR без Смоленской'!$A$4:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>1896</c:v>
                 </c:pt>
@@ -3488,75 +5035,69 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1913</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1914</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'все вместе'!$B$4:$B$22</c:f>
+              <c:f>'BR без Смоленской'!$B$4:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>53</c:v>
+                  <c:v>45.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53</c:v>
+                  <c:v>45.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.7</c:v>
+                  <c:v>44.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.4</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52.1</c:v>
+                  <c:v>46.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51.7</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52.6</c:v>
+                  <c:v>46.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>52.2</c:v>
+                  <c:v>41.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.5</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.7</c:v>
+                  <c:v>40.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.4</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.4</c:v>
+                  <c:v>42.8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>49.8</c:v>
+                  <c:v>39.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>50.1</c:v>
+                  <c:v>39.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>51</c:v>
+                  <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.7</c:v>
+                  <c:v>39.299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.7</c:v>
+                  <c:v>39.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>48.3</c:v>
+                  <c:v>38.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3564,571 +5105,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6912-4F2C-AF86-A269FE454EE3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'все вместе'!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Новороссия</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'все вместе'!$A$4:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>1896</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1897</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1898</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1899</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1901</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1902</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1903</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1904</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1905</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1906</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1907</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1908</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1909</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1910</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1911</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1912</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1913</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1914</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'все вместе'!$C$4:$C$22</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>52.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>51.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50.4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>51.2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>50.4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>46.8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>50.4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>50.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>50.1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>45.9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46.9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>50.2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>47.6</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>48.8</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>48.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>47.9</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>46.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6912-4F2C-AF86-A269FE454EE3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'все вместе'!$D$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Малороссия</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="00B050"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="00B050"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'все вместе'!$A$4:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>1896</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1897</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1898</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1899</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1901</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1902</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1903</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1904</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1905</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1906</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1907</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1908</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1909</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1910</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1911</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1912</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1913</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1914</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'все вместе'!$D$4:$D$22</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>48.9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>48.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46.2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>47.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>44.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>44.2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>41.4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>43.3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>44.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>42.2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>41.2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>40.9</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>41.4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>41.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>38.799999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6912-4F2C-AF86-A269FE454EE3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'все вместе'!$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Белоруссия</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'все вместе'!$A$4:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>1896</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1897</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1898</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1899</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1900</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1901</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1902</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1903</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1904</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1905</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1906</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1907</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1908</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1909</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1910</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1911</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1912</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1913</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1914</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'все вместе'!$E$4:$E$22</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>46.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>46.9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>45.8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46.7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.7</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>45.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>48.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>43.4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>45.3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>41.8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>43.8</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>44.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>41.1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>41.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>41.2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>41.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>40.799999999999997</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>40.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-6912-4F2C-AF86-A269FE454EE3}"/>
+              <c16:uniqueId val="{00000001-4CE8-4E6E-AC1B-C5BB196D6397}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4140,14 +5117,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="733148016"/>
-        <c:axId val="733147688"/>
+        <c:axId val="445026464"/>
+        <c:axId val="445036544"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="733148016"/>
+        <c:axId val="445026464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1914"/>
           <c:min val="1896"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4203,14 +5179,15 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="733147688"/>
+        <c:crossAx val="445036544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="733147688"/>
+        <c:axId val="445036544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="48"/>
           <c:min val="38"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4266,7 +5243,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="733148016"/>
+        <c:crossAx val="445026464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4280,13 +5257,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -4319,11 +5289,90 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5199,6 +6248,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -9639,13 +11720,94 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>952</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB3AEA5-BD15-467B-BEF4-A5D09128FC2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>618172</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27621</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2849284C-00FD-406A-99A8-C42692623B64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>14287</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -9676,7 +11838,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -9771,11 +11933,11 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.71881</cdr:x>
-      <cdr:y>0.85935</cdr:y>
+      <cdr:y>0.8262</cdr:y>
     </cdr:from>
     <cdr:to>
       <cdr:x>0.83281</cdr:x>
-      <cdr:y>0.89837</cdr:y>
+      <cdr:y>0.86114</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -9790,8 +11952,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5405438" y="9020175"/>
-          <a:ext cx="857250" cy="409574"/>
+          <a:off x="5405443" y="9010651"/>
+          <a:ext cx="857278" cy="380999"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -9850,6 +12012,70 @@
             <a:rPr lang="ru-RU" sz="1600" b="1"/>
             <a:t>РСФСР-1991</a:t>
           </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.49082</cdr:x>
+      <cdr:y>0.9083</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.61241</cdr:x>
+      <cdr:y>0.99214</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12D6A69F-6875-409C-976E-205FD2D29DAF}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3690938" y="9906000"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Белоруссия</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> без Смоленской</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1600" b="1">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </cdr:txBody>
     </cdr:sp>
@@ -10340,15 +12566,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C22">TREND($B$4:$B$22,$A$4:$A$22,A4:A22)</f>
-        <v>52.816315789473663</v>
+        <v>53.126842105263165</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.20824561403509279</v>
+        <v>0.21701754385964023</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -10360,10 +12586,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="C5" s="6">
-        <v>52.60807017543857</v>
+        <v>52.909824561403525</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -10375,11 +12601,11 @@
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.39428273426939597</v>
+        <v>0.40848944763109785</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.39428273426928229</v>
+        <v>0.40848944763122574</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -10388,10 +12614,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6">
-        <v>52.399824561403534</v>
+        <v>52.692807017543828</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -10399,11 +12625,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>4.3396226415094361</v>
+        <v>4.3151969981238238</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U22" si="2">100 - 100 * C6/$C$4</f>
-        <v>0.78856546853867826</v>
+        <v>0.81697889526232359</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -10412,10 +12638,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="C7" s="6">
-        <v>52.191578947368441</v>
+        <v>52.475789473684188</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -10423,11 +12649,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T22" si="3">100 - 100 * B7/$B$4</f>
-        <v>3.0188679245283083</v>
+        <v>3.0018761726078793</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>1.18284820280806</v>
+        <v>1.2254683428934214</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -10436,10 +12662,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
       <c r="C8" s="6">
-        <v>51.983333333333348</v>
+        <v>52.258771929824547</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -10447,11 +12673,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>1.6981132075471663</v>
+        <v>1.6885553470919206</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>1.577130937077456</v>
+        <v>1.6339577905245477</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -10460,10 +12686,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="C9" s="6">
-        <v>51.775087719298256</v>
+        <v>52.041754385964907</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -10471,11 +12697,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>2.4528301886792434</v>
+        <v>2.4390243902439011</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>1.971413671346852</v>
+        <v>2.0424472381556456</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -10484,10 +12710,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="C10" s="6">
-        <v>51.566842105263163</v>
+        <v>51.824736842105267</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -10495,11 +12721,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>0.75471698113207708</v>
+        <v>0.93808630393995429</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>2.3656964056162337</v>
+        <v>2.4509366857867576</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -10508,10 +12734,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="C11" s="6">
-        <v>51.35859649122807</v>
+        <v>51.607719298245627</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -10519,11 +12745,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>1.5094339622641542</v>
+        <v>1.5009380863039326</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>2.7599791398856297</v>
+        <v>2.8594261334178555</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -10532,10 +12758,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="C12" s="6">
-        <v>51.150350877192977</v>
+        <v>51.39070175438593</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -10543,11 +12769,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>0.94339622641508925</v>
+        <v>1.1257035647279565</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>3.1542618741550257</v>
+        <v>3.2679155810490812</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -10556,10 +12782,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="C13" s="6">
-        <v>50.942105263157885</v>
+        <v>51.173684210526289</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -10567,11 +12793,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>8.1132075471698073</v>
+        <v>8.2551594746716717</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>3.5485446084244217</v>
+        <v>3.676405028680179</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -10580,10 +12806,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="C14" s="6">
-        <v>50.733859649122792</v>
+        <v>50.956666666666649</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -10591,11 +12817,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>3.0188679245283083</v>
+        <v>3.1894934333958673</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>3.9428273426938034</v>
+        <v>4.0848944763112911</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -10604,10 +12830,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="C15" s="6">
-        <v>50.525614035087699</v>
+        <v>50.739649122807009</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -10615,11 +12841,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="3"/>
-        <v>3.0188679245283083</v>
+        <v>3.1894934333958673</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>4.3371100769631852</v>
+        <v>4.4933839239424032</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -10628,10 +12854,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="C16" s="6">
-        <v>50.317368421052606</v>
+        <v>50.522631578947369</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -10639,11 +12865,11 @@
       </c>
       <c r="T16" s="1">
         <f t="shared" si="3"/>
-        <v>6.0377358490566024</v>
+        <v>6.1913696060037466</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>4.7313928112325812</v>
+        <v>4.9018733715735152</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -10652,10 +12878,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="C17" s="6">
-        <v>50.10912280701757</v>
+        <v>50.305614035087729</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -10663,11 +12889,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>5.4716981132075517</v>
+        <v>5.6285178236397684</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>5.1256755455018634</v>
+        <v>5.3103628192046131</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -10676,10 +12902,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="C18" s="6">
-        <v>49.900877192982477</v>
+        <v>50.088596491228088</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -10687,11 +12913,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>3.7735849056603712</v>
+        <v>3.9399624765478336</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>5.5199582797712594</v>
+        <v>5.7188522668357109</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -10700,10 +12926,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="C19" s="6">
-        <v>49.692631578947385</v>
+        <v>49.871578947368391</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -10711,11 +12937,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>4.3396226415094361</v>
+        <v>4.5028142589118119</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>5.9142410140406412</v>
+        <v>6.1273417144669367</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -10724,10 +12950,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="C20" s="6">
-        <v>49.484385964912292</v>
+        <v>49.654561403508751</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -10735,11 +12961,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>8.1132075471698073</v>
+        <v>8.2551594746716717</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>6.3085237483100371</v>
+        <v>6.5358311620980487</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -10748,10 +12974,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="C21" s="6">
-        <v>49.276140350877199</v>
+        <v>49.437543859649111</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -10759,11 +12985,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>8.3018867924528337</v>
+        <v>8.4427767354596597</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>6.7028064825794331</v>
+        <v>6.9443206097291466</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -10771,21 +12997,21 @@
         <v>1914</v>
       </c>
       <c r="B22" s="5">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="C22" s="6">
-        <v>49.067894736842106</v>
+        <v>49.220526315789471</v>
       </c>
       <c r="S22" s="4">
         <v>1914</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" si="3"/>
-        <v>8.8679245283018844</v>
+        <v>9.193245778611626</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="2"/>
-        <v>7.0970892168488149</v>
+        <v>7.3528100573602728</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -10795,7 +13021,7 @@
       </c>
       <c r="C23" s="6">
         <f>C22-$D$4</f>
-        <v>48.859649122807014</v>
+        <v>49.00350877192983</v>
       </c>
       <c r="S23" s="4">
         <f>S22+1</f>
@@ -10803,7 +13029,7 @@
       </c>
       <c r="U23" s="6">
         <f t="shared" ref="U23:U35" si="5">U22+STEP</f>
-        <v>7.5746258865250695</v>
+        <v>7.8303467270365275</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -10813,7 +13039,7 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" ref="C24:C29" si="6">C23-$D$4</f>
-        <v>48.651403508771921</v>
+        <v>48.78649122807019</v>
       </c>
       <c r="S24" s="4">
         <f t="shared" ref="S24:S35" si="7">S23+1</f>
@@ -10821,7 +13047,7 @@
       </c>
       <c r="U24" s="6">
         <f t="shared" si="5"/>
-        <v>8.0521625562013242</v>
+        <v>8.3078833967127821</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -10831,7 +13057,7 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="6"/>
-        <v>48.443157894736828</v>
+        <v>48.56947368421055</v>
       </c>
       <c r="S25" s="4">
         <f t="shared" si="7"/>
@@ -10839,7 +13065,7 @@
       </c>
       <c r="U25" s="6">
         <f t="shared" si="5"/>
-        <v>8.5296992258775788</v>
+        <v>8.7854200663890367</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -10849,7 +13075,7 @@
       </c>
       <c r="C26" s="6">
         <f t="shared" si="6"/>
-        <v>48.234912280701735</v>
+        <v>48.35245614035091</v>
       </c>
       <c r="S26" s="4">
         <f t="shared" si="7"/>
@@ -10857,7 +13083,7 @@
       </c>
       <c r="U26" s="6">
         <f t="shared" si="5"/>
-        <v>9.0072358955538334</v>
+        <v>9.2629567360652914</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -10867,7 +13093,7 @@
       </c>
       <c r="C27" s="6">
         <f t="shared" si="6"/>
-        <v>48.026666666666642</v>
+        <v>48.135438596491269</v>
       </c>
       <c r="S27" s="4">
         <f t="shared" si="7"/>
@@ -10875,7 +13101,7 @@
       </c>
       <c r="U27" s="6">
         <f t="shared" si="5"/>
-        <v>9.484772565230088</v>
+        <v>9.740493405741546</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -10885,7 +13111,7 @@
       </c>
       <c r="C28" s="6">
         <f t="shared" si="6"/>
-        <v>47.81842105263155</v>
+        <v>47.918421052631629</v>
       </c>
       <c r="S28" s="4">
         <f t="shared" si="7"/>
@@ -10893,7 +13119,7 @@
       </c>
       <c r="U28" s="12">
         <f t="shared" si="5"/>
-        <v>9.9623092349063427</v>
+        <v>10.218030075417801</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -10903,7 +13129,7 @@
       </c>
       <c r="C29" s="6">
         <f t="shared" si="6"/>
-        <v>47.610175438596457</v>
+        <v>47.701403508771989</v>
       </c>
       <c r="S29" s="7">
         <f t="shared" si="7"/>
@@ -10912,7 +13138,7 @@
       <c r="T29" s="9"/>
       <c r="U29" s="12">
         <f t="shared" si="5"/>
-        <v>10.439845904582597</v>
+        <v>10.695566745094055</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -10922,7 +13148,7 @@
       </c>
       <c r="U30" s="6">
         <f t="shared" si="5"/>
-        <v>10.917382574258852</v>
+        <v>11.17310341477031</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -10932,7 +13158,7 @@
       </c>
       <c r="U31" s="6">
         <f t="shared" si="5"/>
-        <v>11.394919243935107</v>
+        <v>11.650640084446565</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -10942,7 +13168,7 @@
       </c>
       <c r="U32" s="6">
         <f t="shared" si="5"/>
-        <v>11.872455913611361</v>
+        <v>12.128176754122819</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -10952,7 +13178,7 @@
       </c>
       <c r="U33" s="6">
         <f t="shared" si="5"/>
-        <v>12.349992583287616</v>
+        <v>12.605713423799074</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -10962,7 +13188,7 @@
       </c>
       <c r="U34" s="6">
         <f t="shared" si="5"/>
-        <v>12.82752925296387</v>
+        <v>13.083250093475328</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -10972,7 +13198,7 @@
       </c>
       <c r="U35" s="6">
         <f t="shared" si="5"/>
-        <v>13.305065922640125</v>
+        <v>13.560786763151583</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15">
@@ -10993,7 +13219,7 @@
         <v>1896</v>
       </c>
       <c r="B42" s="5">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -11002,7 +13228,7 @@
         <v>1897</v>
       </c>
       <c r="B43" s="5">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -11018,7 +13244,7 @@
         <v>1899</v>
       </c>
       <c r="B45" s="5">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -11027,7 +13253,7 @@
         <v>1900</v>
       </c>
       <c r="B46" s="5">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -11036,7 +13262,7 @@
         <v>1901</v>
       </c>
       <c r="B47" s="5">
-        <v>51.7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -11045,7 +13271,7 @@
         <v>1902</v>
       </c>
       <c r="B48" s="5">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -11054,7 +13280,7 @@
         <v>1903</v>
       </c>
       <c r="B49" s="5">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -11063,7 +13289,7 @@
         <v>1904</v>
       </c>
       <c r="B50" s="5">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -11079,7 +13305,7 @@
         <v>1906</v>
       </c>
       <c r="B52" s="5">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -11088,7 +13314,7 @@
         <v>1907</v>
       </c>
       <c r="B53" s="5">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -11118,7 +13344,7 @@
         <v>1911</v>
       </c>
       <c r="B57" s="5">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -11127,7 +13353,7 @@
         <v>1912</v>
       </c>
       <c r="B58" s="5">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -11136,7 +13362,7 @@
         <v>1913</v>
       </c>
       <c r="B59" s="5">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -11144,7 +13370,7 @@
         <v>1914</v>
       </c>
       <c r="B60" s="5">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
     </row>
   </sheetData>
@@ -11155,7 +13381,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F786236-6DB6-44ED-BB49-A78B092F8D0C}">
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -11632,7 +13858,9 @@
         <f>A21+1</f>
         <v>1914</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="5">
+        <v>44.5</v>
+      </c>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
         <v>46.735947712418238</v>
@@ -11739,7 +13967,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="4">
-        <f t="shared" ref="A34:A49" si="5">A33+1</f>
+        <f t="shared" ref="A34:A50" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
@@ -11869,6 +14097,15 @@
       </c>
       <c r="B49" s="5">
         <v>46.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="4">
+        <f t="shared" si="5"/>
+        <v>1914</v>
+      </c>
+      <c r="B50" s="4">
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -11930,11 +14167,11 @@
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>48.453216374269005</v>
+        <v>48.443859649122828</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.51475748194013704</v>
+        <v>0.51300309597525029</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -11949,7 +14186,7 @@
         <v>48.4</v>
       </c>
       <c r="C5" s="6">
-        <v>47.938458892328867</v>
+        <v>47.930856553147578</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -11961,11 +14198,11 @@
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>1.0623804165320507</v>
+        <v>1.0589641281493982</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>1.0623804165320649</v>
+        <v>1.058964128149384</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -11977,7 +14214,7 @@
         <v>46.2</v>
       </c>
       <c r="C6" s="6">
-        <v>47.42370141038873</v>
+        <v>47.417853457172328</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -11989,7 +14226,7 @@
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>2.1247608330641157</v>
+        <v>2.1179282562987822</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -12001,7 +14238,7 @@
         <v>47.6</v>
       </c>
       <c r="C7" s="6">
-        <v>46.908943928448593</v>
+        <v>46.904850361197077</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -12013,7 +14250,7 @@
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>3.1871412495961806</v>
+        <v>3.1768923844481805</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -12025,7 +14262,7 @@
         <v>47.9</v>
       </c>
       <c r="C8" s="6">
-        <v>46.394186446508456</v>
+        <v>46.391847265221941</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -12037,7 +14274,7 @@
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>4.2495216661282171</v>
+        <v>4.2358565125973513</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -12049,7 +14286,7 @@
         <v>44</v>
       </c>
       <c r="C9" s="6">
-        <v>45.879428964568319</v>
+        <v>45.87884416924669</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -12061,7 +14298,7 @@
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>5.3119020826602679</v>
+        <v>5.2948206407467353</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -12073,7 +14310,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="6">
-        <v>45.364671482628182</v>
+        <v>45.36584107327144</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -12085,7 +14322,7 @@
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>6.3742824991923328</v>
+        <v>6.3537847688961335</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -12097,7 +14334,7 @@
         <v>44.9</v>
       </c>
       <c r="C11" s="6">
-        <v>44.849914000687932</v>
+        <v>44.85283797729619</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -12109,7 +14346,7 @@
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>7.4366629157246251</v>
+        <v>7.412748897045546</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -12121,7 +14358,7 @@
         <v>44.2</v>
       </c>
       <c r="C12" s="6">
-        <v>44.335156518747795</v>
+        <v>44.33983488132094</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -12133,7 +14370,7 @@
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>8.4990433322566901</v>
+        <v>8.47171302519493</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -12145,7 +14382,7 @@
         <v>41.4</v>
       </c>
       <c r="C13" s="6">
-        <v>43.820399036807657</v>
+        <v>43.826831785345689</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -12157,7 +14394,7 @@
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>9.5614237487887266</v>
+        <v>9.530677153344314</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -12169,7 +14406,7 @@
         <v>43.3</v>
       </c>
       <c r="C14" s="6">
-        <v>43.30564155486752</v>
+        <v>43.313828689370553</v>
       </c>
       <c r="S14" s="7">
         <f t="shared" si="1"/>
@@ -12181,7 +14418,7 @@
       </c>
       <c r="U14" s="12">
         <f t="shared" si="2"/>
-        <v>10.623804165320777</v>
+        <v>10.589641281493499</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -12193,7 +14430,7 @@
         <v>44.6</v>
       </c>
       <c r="C15" s="6">
-        <v>42.790884072927383</v>
+        <v>42.800825593395302</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -12205,7 +14442,7 @@
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>11.686184581852842</v>
+        <v>11.648605409642883</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -12217,7 +14454,7 @@
         <v>42.2</v>
       </c>
       <c r="C16" s="6">
-        <v>42.276126590987246</v>
+        <v>42.287822497420052</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -12229,7 +14466,7 @@
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>12.748564998384907</v>
+        <v>12.707569537792267</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -12241,7 +14478,7 @@
         <v>41.2</v>
       </c>
       <c r="C17" s="6">
-        <v>41.761369109047109</v>
+        <v>41.774819401444802</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -12253,7 +14490,7 @@
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>13.810945414916958</v>
+        <v>13.766533665941665</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -12265,7 +14502,7 @@
         <v>40.9</v>
       </c>
       <c r="C18" s="6">
-        <v>41.246611627106972</v>
+        <v>41.261816305469551</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -12277,7 +14514,7 @@
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>14.873325831448994</v>
+        <v>14.825497794091078</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -12289,7 +14526,7 @@
         <v>41.4</v>
       </c>
       <c r="C19" s="6">
-        <v>40.731854145166835</v>
+        <v>40.748813209494301</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -12301,7 +14538,7 @@
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>15.935706247981059</v>
+        <v>15.884461922240462</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -12313,7 +14550,7 @@
         <v>41.5</v>
       </c>
       <c r="C20" s="6">
-        <v>40.217096663226698</v>
+        <v>40.235810113519051</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -12325,7 +14562,7 @@
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>16.998086664513124</v>
+        <v>16.94342605038986</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -12334,10 +14571,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>38.799999999999997</v>
+        <v>38.9</v>
       </c>
       <c r="C21" s="6">
-        <v>39.702339181286561</v>
+        <v>39.722807017543914</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -12345,11 +14582,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>20.654396728016366</v>
+        <v>20.449897750511241</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>18.060467081045175</v>
+        <v>18.002390178539017</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -12360,7 +14597,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
-        <v>39.187581699346424</v>
+        <v>39.209803921568664</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -12370,7 +14607,7 @@
       </c>
       <c r="C23" s="6">
         <f>C22-$D$4</f>
-        <v>38.672824217406287</v>
+        <v>38.696800825593414</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -12380,7 +14617,7 @@
       </c>
       <c r="C24" s="6">
         <f>C23-$D$4</f>
-        <v>38.15806673546615</v>
+        <v>38.183797729618163</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -12390,7 +14627,7 @@
       </c>
       <c r="C25" s="6">
         <f>C24-$D$4</f>
-        <v>37.643309253526013</v>
+        <v>37.670794633642913</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15">
@@ -12554,7 +14791,7 @@
         <v>1913</v>
       </c>
       <c r="B48" s="5">
-        <v>38.799999999999997</v>
+        <v>38.9</v>
       </c>
     </row>
   </sheetData>
@@ -12578,7 +14815,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="18">
       <c r="A1" s="10" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15">
@@ -12905,15 +15142,15 @@
       <c r="C16" s="6">
         <v>42.540522875817032</v>
       </c>
-      <c r="S16" s="4">
+      <c r="S16" s="7">
         <f t="shared" si="1"/>
         <v>1908</v>
       </c>
-      <c r="T16" s="1">
+      <c r="T16" s="8">
         <f t="shared" si="3"/>
         <v>11.612903225806448</v>
       </c>
-      <c r="U16" s="6">
+      <c r="U16" s="12">
         <f t="shared" si="2"/>
         <v>11.023772744049936</v>
       </c>
@@ -13250,8 +15487,693 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D442F504-F5DF-44D0-8AAF-FB92847F2F5A}">
+  <dimension ref="A1:V49"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="20" max="20" width="22.625" customWidth="1"/>
+    <col min="21" max="21" width="21.25" customWidth="1"/>
+    <col min="22" max="22" width="24.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="18">
+      <c r="A1" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="4">
+        <v>1896</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45.1</v>
+      </c>
+      <c r="C4" s="6" cm="1">
+        <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
+        <v>46.139181286549729</v>
+      </c>
+      <c r="D4" s="6">
+        <f>C4-C5</f>
+        <v>0.45036119711051015</v>
+      </c>
+      <c r="S4" s="4">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="4">
+        <f>A4+1</f>
+        <v>1897</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45.1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>45.688820089439218</v>
+      </c>
+      <c r="S5" s="4">
+        <f>S4+1</f>
+        <v>1897</v>
+      </c>
+      <c r="T5" s="1">
+        <f>100 - 100 * B5/$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <f>100 - 100 * C5/$C$4</f>
+        <v>0.97609273626578386</v>
+      </c>
+      <c r="V5" s="6">
+        <f>U6-U5</f>
+        <v>0.97609273626552806</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="4">
+        <f t="shared" ref="A6:A21" si="0">A5+1</f>
+        <v>1898</v>
+      </c>
+      <c r="B6" s="5">
+        <v>44.1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>45.238458892328822</v>
+      </c>
+      <c r="S6" s="4">
+        <f t="shared" ref="S6:S21" si="1">S5+1</f>
+        <v>1898</v>
+      </c>
+      <c r="T6" s="1">
+        <f>100 - 100 * B6/$B$4</f>
+        <v>2.2172949002217308</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
+        <v>1.9521854725313119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="4">
+        <f t="shared" si="0"/>
+        <v>1899</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45</v>
+      </c>
+      <c r="C7" s="6">
+        <v>44.788097695218426</v>
+      </c>
+      <c r="S7" s="4">
+        <f t="shared" si="1"/>
+        <v>1899</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
+        <v>0.22172949002217024</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="2"/>
+        <v>2.92827820879684</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46.1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>44.337736498108029</v>
+      </c>
+      <c r="S8" s="4">
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" si="3"/>
+        <v>-2.2172949002217308</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="2"/>
+        <v>3.904370945062368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>1901</v>
+      </c>
+      <c r="B9" s="5">
+        <v>44</v>
+      </c>
+      <c r="C9" s="6">
+        <v>43.887375300997633</v>
+      </c>
+      <c r="S9" s="4">
+        <f t="shared" si="1"/>
+        <v>1901</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" si="3"/>
+        <v>2.4390243902439011</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="2"/>
+        <v>4.8804636813279103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>1902</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46.8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>43.437014103887122</v>
+      </c>
+      <c r="S10" s="4">
+        <f t="shared" si="1"/>
+        <v>1902</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" si="3"/>
+        <v>-3.7694013303769367</v>
+      </c>
+      <c r="U10" s="6">
+        <f t="shared" si="2"/>
+        <v>5.8565564175936657</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>1903</v>
+      </c>
+      <c r="B11" s="5">
+        <v>41.8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>42.986652906776726</v>
+      </c>
+      <c r="S11" s="4">
+        <f t="shared" si="1"/>
+        <v>1903</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" si="3"/>
+        <v>7.3170731707317032</v>
+      </c>
+      <c r="U11" s="6">
+        <f t="shared" si="2"/>
+        <v>6.8326491538591938</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>1904</v>
+      </c>
+      <c r="B12" s="5">
+        <v>43</v>
+      </c>
+      <c r="C12" s="6">
+        <v>42.53629170966633</v>
+      </c>
+      <c r="S12" s="4">
+        <f t="shared" si="1"/>
+        <v>1904</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" si="3"/>
+        <v>4.6563192904656319</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="2"/>
+        <v>7.8087418901247361</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>1905</v>
+      </c>
+      <c r="B13" s="5">
+        <v>40.4</v>
+      </c>
+      <c r="C13" s="6">
+        <v>42.085930512555933</v>
+      </c>
+      <c r="S13" s="4">
+        <f t="shared" si="1"/>
+        <v>1905</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" si="3"/>
+        <v>10.421286031042129</v>
+      </c>
+      <c r="U13" s="6">
+        <f t="shared" si="2"/>
+        <v>8.7848346263902641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>1906</v>
+      </c>
+      <c r="B14" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="C14" s="6">
+        <v>41.635569315445423</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="1"/>
+        <v>1906</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" si="3"/>
+        <v>7.9822616407982281</v>
+      </c>
+      <c r="U14" s="6">
+        <f t="shared" si="2"/>
+        <v>9.7609273626560196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>1907</v>
+      </c>
+      <c r="B15" s="5">
+        <v>42.8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>41.185208118335026</v>
+      </c>
+      <c r="S15" s="7">
+        <f t="shared" si="1"/>
+        <v>1907</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" si="3"/>
+        <v>5.0997782705099866</v>
+      </c>
+      <c r="U15" s="12">
+        <f t="shared" si="2"/>
+        <v>10.737020098921562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="B16" s="5">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="C16" s="6">
+        <v>40.73484692122463</v>
+      </c>
+      <c r="S16" s="7">
+        <f t="shared" si="1"/>
+        <v>1908</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="3"/>
+        <v>11.973392461197335</v>
+      </c>
+      <c r="U16" s="12">
+        <f t="shared" si="2"/>
+        <v>11.71311283518709</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>1909</v>
+      </c>
+      <c r="B17" s="5">
+        <v>39.9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>40.284485724114234</v>
+      </c>
+      <c r="S17" s="4">
+        <f t="shared" si="1"/>
+        <v>1909</v>
+      </c>
+      <c r="T17" s="1">
+        <f t="shared" si="3"/>
+        <v>11.529933481152995</v>
+      </c>
+      <c r="U17" s="6">
+        <f t="shared" si="2"/>
+        <v>12.689205571452618</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="B18" s="5">
+        <v>39.5</v>
+      </c>
+      <c r="C18" s="6">
+        <v>39.834124527003723</v>
+      </c>
+      <c r="S18" s="4">
+        <f t="shared" si="1"/>
+        <v>1910</v>
+      </c>
+      <c r="T18" s="1">
+        <f t="shared" si="3"/>
+        <v>12.41685144124169</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" si="2"/>
+        <v>13.665298307718402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="B19" s="5">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="C19" s="6">
+        <v>39.383763329893327</v>
+      </c>
+      <c r="S19" s="4">
+        <f t="shared" si="1"/>
+        <v>1911</v>
+      </c>
+      <c r="T19" s="1">
+        <f t="shared" si="3"/>
+        <v>12.860310421286044</v>
+      </c>
+      <c r="U19" s="6">
+        <f t="shared" si="2"/>
+        <v>14.64139104398393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>1912</v>
+      </c>
+      <c r="B20" s="5">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="C20" s="6">
+        <v>38.93340213278293</v>
+      </c>
+      <c r="S20" s="4">
+        <f t="shared" si="1"/>
+        <v>1912</v>
+      </c>
+      <c r="T20" s="1">
+        <f t="shared" si="3"/>
+        <v>13.0820399113082</v>
+      </c>
+      <c r="U20" s="6">
+        <f t="shared" si="2"/>
+        <v>15.617483780249458</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>1913</v>
+      </c>
+      <c r="B21" s="5">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C21" s="6">
+        <v>38.483040935672534</v>
+      </c>
+      <c r="S21" s="4">
+        <f t="shared" si="1"/>
+        <v>1913</v>
+      </c>
+      <c r="T21" s="1">
+        <f t="shared" si="3"/>
+        <v>15.077605321507775</v>
+      </c>
+      <c r="U21" s="6">
+        <f t="shared" si="2"/>
+        <v>16.593576516514986</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="4">
+        <f>A21+1</f>
+        <v>1914</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="6">
+        <f>C21-$D$4</f>
+        <v>38.032679738562024</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="4">
+        <f>A22+1</f>
+        <v>1915</v>
+      </c>
+      <c r="C23" s="6">
+        <f t="shared" ref="C23:C25" si="4">C22-$D$4</f>
+        <v>37.582318541451514</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="4">
+        <f>A23+1</f>
+        <v>1916</v>
+      </c>
+      <c r="C24" s="6">
+        <f t="shared" si="4"/>
+        <v>37.131957344341004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="4">
+        <f>A24+1</f>
+        <v>1917</v>
+      </c>
+      <c r="C25" s="6">
+        <f t="shared" si="4"/>
+        <v>36.681596147230493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15">
+      <c r="A29" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15">
+      <c r="A31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="4">
+        <v>1896</v>
+      </c>
+      <c r="B32" s="5">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="4">
+        <f>A32+1</f>
+        <v>1897</v>
+      </c>
+      <c r="B33" s="5">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="4">
+        <f t="shared" ref="A34:A49" si="5">A33+1</f>
+        <v>1898</v>
+      </c>
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="4">
+        <f t="shared" si="5"/>
+        <v>1899</v>
+      </c>
+      <c r="B35" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="4">
+        <f t="shared" si="5"/>
+        <v>1900</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="4">
+        <f t="shared" si="5"/>
+        <v>1901</v>
+      </c>
+      <c r="B37" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="4">
+        <f t="shared" si="5"/>
+        <v>1902</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="4">
+        <f t="shared" si="5"/>
+        <v>1903</v>
+      </c>
+      <c r="B39" s="5">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="4">
+        <f t="shared" si="5"/>
+        <v>1904</v>
+      </c>
+      <c r="B40" s="5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="4">
+        <f t="shared" si="5"/>
+        <v>1905</v>
+      </c>
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="4">
+        <f t="shared" si="5"/>
+        <v>1906</v>
+      </c>
+      <c r="B42" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="4">
+        <f t="shared" si="5"/>
+        <v>1907</v>
+      </c>
+      <c r="B43" s="5">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="4">
+        <f t="shared" si="5"/>
+        <v>1908</v>
+      </c>
+      <c r="B44" s="5"/>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="4">
+        <f t="shared" si="5"/>
+        <v>1909</v>
+      </c>
+      <c r="B45" s="5"/>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="4">
+        <f t="shared" si="5"/>
+        <v>1910</v>
+      </c>
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="4">
+        <f t="shared" si="5"/>
+        <v>1911</v>
+      </c>
+      <c r="B47" s="5">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="4">
+        <f t="shared" si="5"/>
+        <v>1912</v>
+      </c>
+      <c r="B48" s="5">
+        <v>39.200000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="4">
+        <f t="shared" si="5"/>
+        <v>1913</v>
+      </c>
+      <c r="B49" s="5">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03EEFA1-9E72-4B80-AF4D-F111553A5002}">
-  <dimension ref="A3:E22"/>
+  <dimension ref="A2:F22"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
@@ -13259,359 +16181,514 @@
     <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="15">
+    <row r="2" spans="1:6" ht="15" customHeight="1"/>
+    <row r="3" spans="1:6" ht="47.25" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>53</v>
+        <f>RSFSR!B4</f>
+        <v>53.3</v>
       </c>
       <c r="C4" s="5">
+        <f>NR!B4</f>
         <v>52.1</v>
       </c>
       <c r="D4" s="5">
+        <f>MR!B4</f>
         <v>48.9</v>
       </c>
       <c r="E4" s="5">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <f>F4</f>
+        <v>45.1</v>
+      </c>
+      <c r="F4">
+        <f>'BR без Смоленской'!B4</f>
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>53</v>
+        <f>RSFSR!B5</f>
+        <v>53.3</v>
       </c>
       <c r="C5" s="5">
+        <f>NR!B5</f>
         <v>51.5</v>
       </c>
       <c r="D5" s="5">
+        <f>MR!B5</f>
         <v>48.4</v>
       </c>
       <c r="E5" s="5">
+        <f>BR!B5</f>
         <v>46.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="1">
+        <f>'BR без Смоленской'!B5</f>
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>50.7</v>
+        <f>RSFSR!B6</f>
+        <v>51</v>
       </c>
       <c r="C6" s="5">
+        <f>NR!B6</f>
         <v>50.4</v>
       </c>
       <c r="D6" s="5">
+        <f>MR!B6</f>
         <v>46.2</v>
       </c>
       <c r="E6" s="5">
+        <f>BR!B6</f>
         <v>45.8</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="1">
+        <f>'BR без Смоленской'!B6</f>
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>51.4</v>
+        <f>RSFSR!B7</f>
+        <v>51.7</v>
       </c>
       <c r="C7" s="5">
+        <f>NR!B7</f>
         <v>51.2</v>
       </c>
       <c r="D7" s="5">
+        <f>MR!B7</f>
         <v>47.6</v>
       </c>
       <c r="E7" s="5">
+        <f>BR!B7</f>
         <v>46.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="1">
+        <f>'BR без Смоленской'!B7</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>52.1</v>
+        <f>RSFSR!B8</f>
+        <v>52.4</v>
       </c>
       <c r="C8" s="5">
+        <f>NR!B8</f>
         <v>50.4</v>
       </c>
       <c r="D8" s="5">
+        <f>MR!B8</f>
         <v>47.9</v>
       </c>
       <c r="E8" s="5">
+        <f>BR!B8</f>
         <v>47.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="1">
+        <f>'BR без Смоленской'!B8</f>
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>51.7</v>
+        <f>RSFSR!B9</f>
+        <v>52</v>
       </c>
       <c r="C9" s="5">
+        <f>NR!B9</f>
         <v>46.8</v>
       </c>
       <c r="D9" s="5">
+        <f>MR!B9</f>
         <v>44</v>
       </c>
       <c r="E9" s="5">
+        <f>BR!B9</f>
         <v>45.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="1">
+        <f>'BR без Смоленской'!B9</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>52.6</v>
+        <f>RSFSR!B10</f>
+        <v>52.8</v>
       </c>
       <c r="C10" s="5">
+        <f>NR!B10</f>
         <v>50.4</v>
       </c>
       <c r="D10" s="5">
+        <f>MR!B10</f>
         <v>46</v>
       </c>
       <c r="E10" s="5">
+        <f>BR!B10</f>
         <v>48.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="1">
+        <f>'BR без Смоленской'!B10</f>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>52.2</v>
+        <f>RSFSR!B11</f>
+        <v>52.5</v>
       </c>
       <c r="C11" s="5">
+        <f>NR!B11</f>
         <v>50.1</v>
       </c>
       <c r="D11" s="5">
+        <f>MR!B11</f>
         <v>44.9</v>
       </c>
       <c r="E11" s="5">
+        <f>BR!B11</f>
         <v>43.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="1">
+        <f>'BR без Смоленской'!B11</f>
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>52.5</v>
+        <f>RSFSR!B12</f>
+        <v>52.7</v>
       </c>
       <c r="C12" s="5">
+        <f>NR!B12</f>
         <v>50.1</v>
       </c>
       <c r="D12" s="5">
+        <f>MR!B12</f>
         <v>44.2</v>
       </c>
       <c r="E12" s="5">
+        <f>BR!B12</f>
         <v>45.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="1">
+        <f>'BR без Смоленской'!B12</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>48.7</v>
+        <f>RSFSR!B13</f>
+        <v>48.9</v>
       </c>
       <c r="C13" s="5">
+        <f>NR!B13</f>
         <v>45.9</v>
       </c>
       <c r="D13" s="5">
+        <f>MR!B13</f>
         <v>41.4</v>
       </c>
       <c r="E13" s="5">
+        <f>BR!B13</f>
         <v>41.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="1">
+        <f>'BR без Смоленской'!B13</f>
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>51.4</v>
+        <f>RSFSR!B14</f>
+        <v>51.6</v>
       </c>
       <c r="C14" s="5">
+        <f>NR!B14</f>
         <v>46.9</v>
       </c>
       <c r="D14" s="5">
+        <f>MR!B14</f>
         <v>43.3</v>
       </c>
       <c r="E14" s="5">
+        <f>BR!B14</f>
         <v>43.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="1">
+        <f>'BR без Смоленской'!B14</f>
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>51.4</v>
+        <f>RSFSR!B15</f>
+        <v>51.6</v>
       </c>
       <c r="C15" s="5">
+        <f>NR!B15</f>
         <v>50.2</v>
       </c>
       <c r="D15" s="5">
+        <f>MR!B15</f>
         <v>44.6</v>
       </c>
       <c r="E15" s="5">
+        <f>BR!B15</f>
         <v>44.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="1">
+        <f>'BR без Смоленской'!B15</f>
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>49.8</v>
+        <f>RSFSR!B16</f>
+        <v>50</v>
       </c>
       <c r="C16" s="5">
+        <f>NR!B16</f>
         <v>47.6</v>
       </c>
       <c r="D16" s="5">
+        <f>MR!B16</f>
         <v>42.2</v>
       </c>
       <c r="E16" s="5">
+        <f>BR!B16</f>
         <v>41.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="1">
+        <f>'BR без Смоленской'!B16</f>
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>50.1</v>
+        <f>RSFSR!B17</f>
+        <v>50.3</v>
       </c>
       <c r="C17" s="5">
+        <f>NR!B17</f>
         <v>48.8</v>
       </c>
       <c r="D17" s="5">
+        <f>MR!B17</f>
         <v>41.2</v>
       </c>
       <c r="E17" s="5">
+        <f>BR!B17</f>
         <v>41.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="1">
+        <f>'BR без Смоленской'!B17</f>
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>51</v>
+        <f>RSFSR!B18</f>
+        <v>51.2</v>
       </c>
       <c r="C18" s="5">
+        <f>NR!B18</f>
         <v>48</v>
       </c>
       <c r="D18" s="5">
+        <f>MR!B18</f>
         <v>40.9</v>
       </c>
       <c r="E18" s="5">
+        <f>BR!B18</f>
         <v>41.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="1">
+        <f>'BR без Смоленской'!B18</f>
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>50.7</v>
+        <f>RSFSR!B19</f>
+        <v>50.9</v>
       </c>
       <c r="C19" s="5">
+        <f>NR!B19</f>
         <v>48.2</v>
       </c>
       <c r="D19" s="5">
+        <f>MR!B19</f>
         <v>41.4</v>
       </c>
       <c r="E19" s="5">
+        <f>BR!B19</f>
         <v>41.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="1">
+        <f>'BR без Смоленской'!B19</f>
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>48.7</v>
+        <f>RSFSR!B20</f>
+        <v>48.9</v>
       </c>
       <c r="C20" s="5">
+        <f>NR!B20</f>
         <v>47.9</v>
       </c>
       <c r="D20" s="5">
+        <f>MR!B20</f>
         <v>41.5</v>
       </c>
       <c r="E20" s="5">
+        <f>BR!B20</f>
         <v>40.799999999999997</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="1">
+        <f>'BR без Смоленской'!B20</f>
+        <v>39.200000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>48.6</v>
+        <f>RSFSR!B21</f>
+        <v>48.8</v>
       </c>
       <c r="C21" s="5">
+        <f>NR!B21</f>
         <v>46.5</v>
       </c>
       <c r="D21" s="5">
-        <v>38.799999999999997</v>
+        <f>MR!B21</f>
+        <v>38.9</v>
       </c>
       <c r="E21" s="5">
+        <f>BR!B21</f>
         <v>40.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="1">
+        <f>'BR без Смоленской'!B21</f>
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="4">
         <v>1914</v>
       </c>
       <c r="B22" s="5">
-        <v>48.3</v>
+        <f>RSFSR!B22</f>
+        <v>48.4</v>
+      </c>
+      <c r="C22" s="5">
+        <f>NR!B22</f>
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/workbooks/start-of-demographic-transition-ru.xlsx
+++ b/workbooks/start-of-demographic-transition-ru.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D2F907-E687-4AA9-A975-E42F02DEE101}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E38DDC-6160-4653-84F9-1670E7D39443}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="6" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
+    <workbookView xWindow="1545" yWindow="750" windowWidth="25635" windowHeight="21885" activeTab="1" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="5" r:id="rId1"/>
@@ -440,61 +440,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>53.3</c:v>
+                  <c:v>52.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.3</c:v>
+                  <c:v>52.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51</c:v>
+                  <c:v>50.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.7</c:v>
+                  <c:v>51.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>51.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>52.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>52</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>52.8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>52.5</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.7</c:v>
+                  <c:v>52.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.9</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.6</c:v>
+                  <c:v>51.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.6</c:v>
+                  <c:v>51.1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>50</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>50.3</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>51.2</c:v>
+                  <c:v>50.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.9</c:v>
+                  <c:v>50.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.9</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.8</c:v>
+                  <c:v>48.4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48.4</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1203,61 +1203,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>53.3</c:v>
+                  <c:v>52.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.3</c:v>
+                  <c:v>52.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51</c:v>
+                  <c:v>50.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.7</c:v>
+                  <c:v>51.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>51.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>52.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>52</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>52.8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>52.5</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.7</c:v>
+                  <c:v>52.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>48.9</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.6</c:v>
+                  <c:v>51.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.6</c:v>
+                  <c:v>51.1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>50</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>50.3</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>51.2</c:v>
+                  <c:v>50.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>50.9</c:v>
+                  <c:v>50.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.9</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>48.8</c:v>
+                  <c:v>48.4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>48.4</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1394,61 +1394,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>52.1</c:v>
+                  <c:v>51.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.5</c:v>
+                  <c:v>50.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.4</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.2</c:v>
+                  <c:v>50.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50.4</c:v>
+                  <c:v>49.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.8</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.4</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50.1</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50.1</c:v>
+                  <c:v>49.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>45.9</c:v>
+                  <c:v>45.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46.9</c:v>
+                  <c:v>46.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50.2</c:v>
+                  <c:v>49.8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>47.6</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>48.8</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>48</c:v>
+                  <c:v>47.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>48.2</c:v>
+                  <c:v>47.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>47.9</c:v>
+                  <c:v>47.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46.5</c:v>
+                  <c:v>46.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>44.5</c:v>
+                  <c:v>44.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1585,58 +1585,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>48.9</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.4</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46.2</c:v>
+                  <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47.6</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.9</c:v>
+                  <c:v>47.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44</c:v>
+                  <c:v>43.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46</c:v>
+                  <c:v>45.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44.9</c:v>
+                  <c:v>44.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44.2</c:v>
+                  <c:v>43.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.4</c:v>
+                  <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.3</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44.6</c:v>
+                  <c:v>44.3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>42.2</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41.2</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.9</c:v>
+                  <c:v>40.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.4</c:v>
+                  <c:v>41.1</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41.5</c:v>
+                  <c:v>41.1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.9</c:v>
+                  <c:v>38.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1773,58 +1773,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>45.1</c:v>
+                  <c:v>44.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46.9</c:v>
+                  <c:v>46.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45.8</c:v>
+                  <c:v>45.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.7</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.7</c:v>
+                  <c:v>47.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45.7</c:v>
+                  <c:v>45.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>48.9</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.4</c:v>
+                  <c:v>43.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45.3</c:v>
+                  <c:v>44.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.8</c:v>
+                  <c:v>41.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.8</c:v>
+                  <c:v>43.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44.6</c:v>
+                  <c:v>44.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>41.1</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41.5</c:v>
+                  <c:v>41.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>41.2</c:v>
+                  <c:v>40.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.2</c:v>
+                  <c:v>40.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>40.799999999999997</c:v>
+                  <c:v>40.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>40.5</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1950,58 +1950,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>45.1</c:v>
+                  <c:v>44.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.1</c:v>
+                  <c:v>44.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44.1</c:v>
+                  <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>44.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.1</c:v>
+                  <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44</c:v>
+                  <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.8</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41.8</c:v>
+                  <c:v>41.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>40.4</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>41.5</c:v>
+                  <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42.8</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>39.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>39.700000000000003</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>39.9</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>39.5</c:v>
+                  <c:v>39.299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>39.299999999999997</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39.200000000000003</c:v>
+                  <c:v>38.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.299999999999997</c:v>
+                  <c:v>38.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2756,61 +2756,61 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>52.1</c:v>
+                  <c:v>51.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.5</c:v>
+                  <c:v>50.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.4</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.2</c:v>
+                  <c:v>50.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>50.4</c:v>
+                  <c:v>49.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.8</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50.4</c:v>
+                  <c:v>49.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>50.1</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50.1</c:v>
+                  <c:v>49.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>45.9</c:v>
+                  <c:v>45.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46.9</c:v>
+                  <c:v>46.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50.2</c:v>
+                  <c:v>49.8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>47.6</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>48.8</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>48</c:v>
+                  <c:v>47.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>48.2</c:v>
+                  <c:v>47.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>47.9</c:v>
+                  <c:v>47.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46.5</c:v>
+                  <c:v>46.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>44.5</c:v>
+                  <c:v>44.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3530,58 +3530,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>48.9</c:v>
+                  <c:v>48.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48.4</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46.2</c:v>
+                  <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47.6</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.9</c:v>
+                  <c:v>47.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44</c:v>
+                  <c:v>43.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46</c:v>
+                  <c:v>45.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44.9</c:v>
+                  <c:v>44.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44.2</c:v>
+                  <c:v>43.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.4</c:v>
+                  <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.3</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44.6</c:v>
+                  <c:v>44.3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>42.2</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41.2</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.9</c:v>
+                  <c:v>40.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.4</c:v>
+                  <c:v>41.1</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41.5</c:v>
+                  <c:v>41.1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.9</c:v>
+                  <c:v>38.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4288,58 +4288,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>46.5</c:v>
+                  <c:v>46.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46.9</c:v>
+                  <c:v>46.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45.8</c:v>
+                  <c:v>45.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.7</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.7</c:v>
+                  <c:v>47.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45.7</c:v>
+                  <c:v>45.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>48.9</c:v>
+                  <c:v>48.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.4</c:v>
+                  <c:v>43.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45.3</c:v>
+                  <c:v>44.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>41.8</c:v>
+                  <c:v>41.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>43.8</c:v>
+                  <c:v>43.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44.6</c:v>
+                  <c:v>44.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>41.1</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41.5</c:v>
+                  <c:v>41.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>41.2</c:v>
+                  <c:v>40.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.2</c:v>
+                  <c:v>40.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>40.799999999999997</c:v>
+                  <c:v>40.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>40.5</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5046,58 +5046,58 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>45.1</c:v>
+                  <c:v>44.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.1</c:v>
+                  <c:v>44.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44.1</c:v>
+                  <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>44.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.1</c:v>
+                  <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44</c:v>
+                  <c:v>43.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.8</c:v>
+                  <c:v>46.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41.8</c:v>
+                  <c:v>41.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>40.4</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>41.5</c:v>
+                  <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>42.8</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>39.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>39.700000000000003</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>39.9</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>39.5</c:v>
+                  <c:v>39.299999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>39.299999999999997</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39.200000000000003</c:v>
+                  <c:v>38.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38.299999999999997</c:v>
+                  <c:v>38.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12566,15 +12566,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C22">TREND($B$4:$B$22,$A$4:$A$22,A4:A22)</f>
-        <v>53.126842105263165</v>
+        <v>52.657368421052638</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.21701754385964023</v>
+        <v>0.21456140350881014</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -12586,10 +12586,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
       <c r="C5" s="6">
-        <v>52.909824561403525</v>
+        <v>52.442807017543828</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -12597,15 +12597,15 @@
       </c>
       <c r="T5" s="1">
         <f>100 - 100 * B5/$B$4</f>
-        <v>0</v>
+        <v>0.18903591682419574</v>
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.40848944763109785</v>
+        <v>0.40746700783290635</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.40848944763122574</v>
+        <v>0.40746700783277845</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -12614,10 +12614,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="C6" s="6">
-        <v>52.692807017543828</v>
+        <v>52.228245614035075</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -12625,11 +12625,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>4.3151969981238238</v>
+        <v>4.3478260869565162</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U22" si="2">100 - 100 * C6/$C$4</f>
-        <v>0.81697889526232359</v>
+        <v>0.8149340156656848</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -12638,10 +12638,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="C7" s="6">
-        <v>52.475789473684188</v>
+        <v>52.013684210526321</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -12649,11 +12649,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T22" si="3">100 - 100 * B7/$B$4</f>
-        <v>3.0018761726078793</v>
+        <v>3.2136105860113418</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>1.2254683428934214</v>
+        <v>1.2224010234984917</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -12662,10 +12662,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="C8" s="6">
-        <v>52.258771929824547</v>
+        <v>51.799122807017511</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -12673,11 +12673,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>1.6885553470919206</v>
+        <v>1.8903591682419574</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>1.6339577905245477</v>
+        <v>1.6298680313313838</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -12686,10 +12686,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="C9" s="6">
-        <v>52.041754385964907</v>
+        <v>51.584561403508758</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -12697,11 +12697,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>2.4390243902439011</v>
+        <v>2.6465028355387545</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>2.0424472381556456</v>
+        <v>2.0373350391641765</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -12710,10 +12710,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="C10" s="6">
-        <v>51.824736842105267</v>
+        <v>51.370000000000005</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -12721,11 +12721,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>0.93808630393995429</v>
+        <v>0.94517958412097869</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>2.4509366857867576</v>
+        <v>2.4448020469969833</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -12734,10 +12734,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="C11" s="6">
-        <v>51.607719298245627</v>
+        <v>51.155438596491251</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -12745,11 +12745,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>1.5009380863039326</v>
+        <v>1.7013232514177616</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>2.8594261334178555</v>
+        <v>2.852269054829776</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -12758,10 +12758,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="C12" s="6">
-        <v>51.39070175438593</v>
+        <v>50.940877192982441</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -12769,11 +12769,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>1.1257035647279565</v>
+        <v>1.3232514177693702</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>3.2679155810490812</v>
+        <v>3.2597360626626681</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -12782,10 +12782,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="C13" s="6">
-        <v>51.173684210526289</v>
+        <v>50.726315789473688</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -12793,11 +12793,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>8.2551594746716717</v>
+        <v>8.1285444234404451</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>3.676405028680179</v>
+        <v>3.667203070495475</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -12806,10 +12806,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="C14" s="6">
-        <v>50.956666666666649</v>
+        <v>50.511754385964934</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -12817,11 +12817,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>3.1894934333958673</v>
+        <v>3.4026465028355375</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>4.0848944763112911</v>
+        <v>4.0746700783282535</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -12830,10 +12830,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="C15" s="6">
-        <v>50.739649122807009</v>
+        <v>50.297192982456124</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -12841,11 +12841,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="3"/>
-        <v>3.1894934333958673</v>
+        <v>3.4026465028355375</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>4.4933839239424032</v>
+        <v>4.4821370861611456</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -12854,10 +12854,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="C16" s="6">
-        <v>50.522631578947369</v>
+        <v>50.082631578947371</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -12865,11 +12865,11 @@
       </c>
       <c r="T16" s="1">
         <f t="shared" si="3"/>
-        <v>6.1913696060037466</v>
+        <v>6.4272211720226835</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>4.9018733715735152</v>
+        <v>4.8896040939939525</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -12878,10 +12878,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="C17" s="6">
-        <v>50.305614035087729</v>
+        <v>49.868070175438618</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -12889,11 +12889,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>5.6285178236397684</v>
+        <v>5.6710775047259006</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>5.3103628192046131</v>
+        <v>5.2970711018267451</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -12902,10 +12902,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="C18" s="6">
-        <v>50.088596491228088</v>
+        <v>49.653508771929808</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -12913,11 +12913,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>3.9399624765478336</v>
+        <v>3.9697542533081247</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>5.7188522668357109</v>
+        <v>5.7045381096596373</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -12926,10 +12926,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="C19" s="6">
-        <v>49.871578947368391</v>
+        <v>49.438947368421054</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -12937,11 +12937,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>4.5028142589118119</v>
+        <v>4.7258979206049077</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>6.1273417144669367</v>
+        <v>6.1120051174924441</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -12950,10 +12950,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="C20" s="6">
-        <v>49.654561403508751</v>
+        <v>49.224385964912301</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -12961,11 +12961,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>8.2551594746716717</v>
+        <v>8.3175803402646409</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>6.5358311620980487</v>
+        <v>6.5194721253252368</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -12974,10 +12974,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="C21" s="6">
-        <v>49.437543859649111</v>
+        <v>49.009824561403491</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -12985,11 +12985,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>8.4427767354596597</v>
+        <v>8.5066162570888508</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>6.9443206097291466</v>
+        <v>6.9269391331581289</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -12997,21 +12997,21 @@
         <v>1914</v>
       </c>
       <c r="B22" s="5">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6">
-        <v>49.220526315789471</v>
+        <v>48.795263157894738</v>
       </c>
       <c r="S22" s="4">
         <v>1914</v>
       </c>
       <c r="T22" s="1">
         <f t="shared" si="3"/>
-        <v>9.193245778611626</v>
+        <v>9.2627599243856338</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="2"/>
-        <v>7.3528100573602728</v>
+        <v>7.3344061409909358</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="C23" s="6">
         <f>C22-$D$4</f>
-        <v>49.00350877192983</v>
+        <v>48.580701754385927</v>
       </c>
       <c r="S23" s="4">
         <f>S22+1</f>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="U23" s="6">
         <f t="shared" ref="U23:U35" si="5">U22+STEP</f>
-        <v>7.8303467270365275</v>
+        <v>7.7856853439623848</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" ref="C24:C29" si="6">C23-$D$4</f>
-        <v>48.78649122807019</v>
+        <v>48.366140350877117</v>
       </c>
       <c r="S24" s="4">
         <f t="shared" ref="S24:S35" si="7">S23+1</f>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="U24" s="6">
         <f t="shared" si="5"/>
-        <v>8.3078833967127821</v>
+        <v>8.2369645469338337</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="6"/>
-        <v>48.56947368421055</v>
+        <v>48.151578947368307</v>
       </c>
       <c r="S25" s="4">
         <f t="shared" si="7"/>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="U25" s="6">
         <f t="shared" si="5"/>
-        <v>8.7854200663890367</v>
+        <v>8.6882437499052827</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="C26" s="6">
         <f t="shared" si="6"/>
-        <v>48.35245614035091</v>
+        <v>47.937017543859497</v>
       </c>
       <c r="S26" s="4">
         <f t="shared" si="7"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="U26" s="6">
         <f t="shared" si="5"/>
-        <v>9.2629567360652914</v>
+        <v>9.1395229528767317</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="C27" s="6">
         <f t="shared" si="6"/>
-        <v>48.135438596491269</v>
+        <v>47.722456140350687</v>
       </c>
       <c r="S27" s="4">
         <f t="shared" si="7"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="U27" s="6">
         <f t="shared" si="5"/>
-        <v>9.740493405741546</v>
+        <v>9.5908021558481806</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="C28" s="6">
         <f t="shared" si="6"/>
-        <v>47.918421052631629</v>
+        <v>47.507894736841877</v>
       </c>
       <c r="S28" s="4">
         <f t="shared" si="7"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="U28" s="12">
         <f t="shared" si="5"/>
-        <v>10.218030075417801</v>
+        <v>10.04208135881963</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="C29" s="6">
         <f t="shared" si="6"/>
-        <v>47.701403508771989</v>
+        <v>47.293333333333067</v>
       </c>
       <c r="S29" s="7">
         <f t="shared" si="7"/>
@@ -13138,7 +13138,7 @@
       <c r="T29" s="9"/>
       <c r="U29" s="12">
         <f t="shared" si="5"/>
-        <v>10.695566745094055</v>
+        <v>10.493360561791079</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="U30" s="6">
         <f t="shared" si="5"/>
-        <v>11.17310341477031</v>
+        <v>10.944639764762528</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="U31" s="6">
         <f t="shared" si="5"/>
-        <v>11.650640084446565</v>
+        <v>11.395918967733977</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="U32" s="6">
         <f t="shared" si="5"/>
-        <v>12.128176754122819</v>
+        <v>11.847198170705425</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="U33" s="6">
         <f t="shared" si="5"/>
-        <v>12.605713423799074</v>
+        <v>12.298477373676874</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="U34" s="6">
         <f t="shared" si="5"/>
-        <v>13.083250093475328</v>
+        <v>12.749756576648323</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="U35" s="6">
         <f t="shared" si="5"/>
-        <v>13.560786763151583</v>
+        <v>13.201035779619772</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15">
@@ -13375,7 +13375,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -13427,15 +13428,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>51.130994152046753</v>
+        <v>50.538596491228134</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.24416924664603812</v>
+        <v>0.2280701754386314</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -13447,10 +13448,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="C5" s="6">
-        <v>50.886824905400715</v>
+        <v>50.310526315789502</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -13458,15 +13459,15 @@
       </c>
       <c r="T5" s="1">
         <f>100 - 100 * B5/$B$4</f>
-        <v>1.1516314779270687</v>
+        <v>1.1650485436893234</v>
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.47753666967624042</v>
+        <v>0.45127920297156265</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.47753666967625463</v>
+        <v>0.45127920297144897</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -13475,10 +13476,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="C6" s="6">
-        <v>50.642655658754677</v>
+        <v>50.082456140350928</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -13486,11 +13487,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>3.2629558541266874</v>
+        <v>3.106796116504853</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>0.95507333935249505</v>
+        <v>0.90255840594301162</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -13499,10 +13500,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="C7" s="6">
-        <v>50.398486412108696</v>
+        <v>49.854385964912353</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -13510,11 +13511,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
-        <v>1.7274472168905959</v>
+        <v>1.7475728155339851</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>1.4326100090286218</v>
+        <v>1.3538376089144748</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -13523,10 +13524,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="C8" s="6">
-        <v>50.154317165462658</v>
+        <v>49.626315789473722</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -13534,11 +13535,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>3.2629558541266874</v>
+        <v>3.3009708737864116</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>1.9101466787048622</v>
+        <v>1.8051168118860517</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -13547,10 +13548,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
       <c r="C9" s="6">
-        <v>49.910147918816619</v>
+        <v>49.398245614035147</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -13558,11 +13559,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>10.172744721689057</v>
+        <v>10.097087378640779</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>2.3876833483811026</v>
+        <v>2.2563960148575006</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -13571,10 +13572,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="C10" s="6">
-        <v>49.665978672170581</v>
+        <v>49.170175438596516</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -13582,11 +13583,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>3.2629558541266874</v>
+        <v>3.106796116504853</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>2.8652200180573288</v>
+        <v>2.7076752178290775</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -13595,10 +13596,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="C11" s="6">
-        <v>49.421809425524543</v>
+        <v>48.942105263157941</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -13606,11 +13607,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>3.8387715930902147</v>
+        <v>3.8834951456310733</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>3.3427566877335835</v>
+        <v>3.1589544208005407</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -13619,10 +13620,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="C12" s="6">
-        <v>49.177640178878562</v>
+        <v>48.714035087719367</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -13630,11 +13631,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>3.8387715930902147</v>
+        <v>3.6893203883495147</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>3.8202933574097102</v>
+        <v>3.6102336237719896</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -13643,10 +13644,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="C13" s="6">
-        <v>48.933470932232524</v>
+        <v>48.485964912280735</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -13654,11 +13655,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>11.900191938579653</v>
+        <v>11.456310679611647</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>4.2978300270859648</v>
+        <v>4.0615128267435523</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -13667,10 +13668,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="C14" s="6">
-        <v>48.689301685586486</v>
+        <v>48.257894736842161</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -13678,11 +13679,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>9.9808061420345524</v>
+        <v>9.5145631067961176</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>4.7753666967621911</v>
+        <v>4.5127920297150013</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -13691,10 +13692,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="C15" s="6">
-        <v>48.445132438940448</v>
+        <v>48.029824561403586</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -13702,11 +13703,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="3"/>
-        <v>3.6468330134356961</v>
+        <v>3.3009708737864116</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>5.2529033664384457</v>
+        <v>4.9640712326864644</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -13715,10 +13716,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
       <c r="C16" s="6">
-        <v>48.20096319229441</v>
+        <v>47.801754385964955</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -13726,11 +13727,11 @@
       </c>
       <c r="T16" s="1">
         <f t="shared" si="3"/>
-        <v>8.6372360844529794</v>
+        <v>8.3495145631067942</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>5.7304400361146719</v>
+        <v>5.4153504356580271</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -13739,10 +13740,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="C17" s="6">
-        <v>47.956793945648428</v>
+        <v>47.57368421052638</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -13750,11 +13751,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>6.3339731285988563</v>
+        <v>5.8252427184466029</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>6.2079767057908271</v>
+        <v>5.8666296386294903</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -13763,10 +13764,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="C18" s="6">
-        <v>47.71262469900239</v>
+        <v>47.345614035087749</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -13774,11 +13775,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>7.8694817658349336</v>
+        <v>7.1844660194174708</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>6.6855133754670533</v>
+        <v>6.3179088416010671</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -13787,10 +13788,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
       <c r="C19" s="6">
-        <v>47.468455452356352</v>
+        <v>47.117543859649174</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -13798,11 +13799,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>7.4856046065259108</v>
+        <v>7.1844660194174708</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>7.1630500451432937</v>
+        <v>6.7691880445725161</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -13811,10 +13812,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
       <c r="C20" s="6">
-        <v>47.224286205710314</v>
+        <v>46.8894736842106</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -13822,11 +13823,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>8.0614203454894522</v>
+        <v>7.9611650485436911</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>7.6405867148195341</v>
+        <v>7.2204672475439793</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -13835,10 +13836,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="C21" s="6">
-        <v>46.980116959064276</v>
+        <v>46.661403508771969</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -13846,11 +13847,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>10.748560460652598</v>
+        <v>10.485436893203882</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>8.1181233844957887</v>
+        <v>7.6717464505155419</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -13859,11 +13860,11 @@
         <v>1914</v>
       </c>
       <c r="B22" s="5">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
-        <v>46.735947712418238</v>
+        <v>46.433333333333337</v>
       </c>
       <c r="S22" s="4">
         <v>1914</v>
@@ -13871,7 +13872,7 @@
       <c r="T22" s="1"/>
       <c r="U22" s="6">
         <f>U21+STEP_NR</f>
-        <v>8.5956600541720434</v>
+        <v>8.1230256534869909</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -13881,14 +13882,14 @@
       </c>
       <c r="C23" s="6">
         <f t="shared" ref="C23:C26" si="4">C22-$D$4</f>
-        <v>46.4917784657722</v>
+        <v>46.205263157894706</v>
       </c>
       <c r="S23" s="4">
         <v>1915</v>
       </c>
       <c r="U23" s="6">
         <f>U22+STEP_NR</f>
-        <v>9.073196723848298</v>
+        <v>8.5743048564584399</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -13898,14 +13899,14 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" si="4"/>
-        <v>46.247609219126161</v>
+        <v>45.977192982456074</v>
       </c>
       <c r="S24" s="4">
         <v>1916</v>
       </c>
       <c r="U24" s="6">
         <f>U23+STEP_NR</f>
-        <v>9.5507333935245526</v>
+        <v>9.0255840594298888</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -13915,14 +13916,14 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="4"/>
-        <v>46.003439972480123</v>
+        <v>45.749122807017443</v>
       </c>
       <c r="S25" s="4">
         <v>1917</v>
       </c>
       <c r="U25" s="12">
         <f>U24+STEP_NR</f>
-        <v>10.028270063200807</v>
+        <v>9.4768632624013378</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -13932,7 +13933,7 @@
       </c>
       <c r="C26" s="6">
         <f t="shared" si="4"/>
-        <v>45.759270725834085</v>
+        <v>45.521052631578812</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15">
@@ -14163,15 +14164,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>48.443859649122828</v>
+        <v>48.038596491228077</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.51300309597525029</v>
+        <v>0.50454076367384459</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -14183,10 +14184,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="C5" s="6">
-        <v>47.930856553147578</v>
+        <v>47.534055727554232</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -14194,15 +14195,15 @@
       </c>
       <c r="T5" s="1">
         <f>100 - 100 * B5/$B$4</f>
-        <v>1.0224948875255535</v>
+        <v>1.2345679012345698</v>
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>1.0589641281493982</v>
+        <v>1.0502820659341552</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>1.058964128149384</v>
+        <v>1.0502820659343968</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -14211,10 +14212,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="C6" s="6">
-        <v>47.417853457172328</v>
+        <v>47.029514963880274</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -14222,11 +14223,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>5.5214723926380316</v>
+        <v>5.7613168724279831</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>2.1179282562987822</v>
+        <v>2.100564131868552</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -14235,10 +14236,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
       <c r="C7" s="6">
-        <v>46.904850361197077</v>
+        <v>46.524974200206429</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -14246,11 +14247,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
-        <v>2.6584867075664533</v>
+        <v>2.8806584362139915</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>3.1768923844481805</v>
+        <v>3.1508461978027071</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -14259,10 +14260,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="C8" s="6">
-        <v>46.391847265221941</v>
+        <v>46.020433436532585</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -14270,11 +14271,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>2.0449897750511212</v>
+        <v>2.2633744855967137</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>4.2358565125973513</v>
+        <v>4.2011282637368765</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -14283,10 +14284,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="C9" s="6">
-        <v>45.87884416924669</v>
+        <v>45.515892672858627</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -14294,11 +14295,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>10.02044989775051</v>
+        <v>10.288065843621396</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>5.2948206407467353</v>
+        <v>5.2514103296712733</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -14307,10 +14308,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="C10" s="6">
-        <v>45.36584107327144</v>
+        <v>45.011351909184782</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -14318,11 +14319,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>5.930470347648253</v>
+        <v>6.3786008230452751</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>6.3537847688961335</v>
+        <v>6.3016923956054427</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -14331,10 +14332,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
       <c r="C11" s="6">
-        <v>44.85283797729619</v>
+        <v>44.506811145510824</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -14342,11 +14343,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>8.1799591002044991</v>
+        <v>8.4362139917695487</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>7.412748897045546</v>
+        <v>7.3519744615398253</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -14355,10 +14356,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
       <c r="C12" s="6">
-        <v>44.33983488132094</v>
+        <v>44.002270381836979</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -14366,11 +14367,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>9.6114519427402882</v>
+        <v>9.8765432098765444</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>8.47171302519493</v>
+        <v>8.4022565274739804</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -14379,10 +14380,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="C13" s="6">
-        <v>43.826831785345689</v>
+        <v>43.497729618163135</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -14390,11 +14391,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>15.337423312883431</v>
+        <v>15.226337448559676</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>9.530677153344314</v>
+        <v>9.4525385934081356</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -14403,10 +14404,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="C14" s="6">
-        <v>43.313828689370553</v>
+        <v>42.993188854489176</v>
       </c>
       <c r="S14" s="7">
         <f t="shared" si="1"/>
@@ -14414,11 +14415,11 @@
       </c>
       <c r="T14" s="8">
         <f t="shared" si="3"/>
-        <v>11.451942740286299</v>
+        <v>11.522633744855966</v>
       </c>
       <c r="U14" s="12">
         <f t="shared" si="2"/>
-        <v>10.589641281493499</v>
+        <v>10.502820659342532</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -14427,10 +14428,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="C15" s="6">
-        <v>42.800825593395302</v>
+        <v>42.488648090815332</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -14438,11 +14439,11 @@
       </c>
       <c r="T15" s="1">
         <f t="shared" si="3"/>
-        <v>8.7934560327198312</v>
+        <v>8.8477366255144005</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>11.648605409642883</v>
+        <v>11.553102725276688</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -14451,10 +14452,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="C16" s="6">
-        <v>42.287822497420052</v>
+        <v>41.984107327141373</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -14462,11 +14463,11 @@
       </c>
       <c r="T16" s="1">
         <f t="shared" si="3"/>
-        <v>13.701431492842531</v>
+        <v>13.580246913580254</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>12.707569537792267</v>
+        <v>12.603384791211084</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -14475,10 +14476,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="C17" s="6">
-        <v>41.774819401444802</v>
+        <v>41.479566563467529</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -14486,11 +14487,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>15.746421267893652</v>
+        <v>15.637860082304528</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>13.766533665941665</v>
+        <v>13.653666857145254</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -14499,10 +14500,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>40.9</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="C18" s="6">
-        <v>41.261816305469551</v>
+        <v>40.975025799793684</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -14510,11 +14511,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>16.359918200408998</v>
+        <v>16.255144032921805</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>14.825497794091078</v>
+        <v>14.703948923079409</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -14523,10 +14524,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="C19" s="6">
-        <v>40.748813209494301</v>
+        <v>40.470485036119726</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -14534,11 +14535,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>15.337423312883431</v>
+        <v>15.432098765432102</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>15.884461922240462</v>
+        <v>15.754230989013806</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -14547,10 +14548,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="C20" s="6">
-        <v>40.235810113519051</v>
+        <v>39.965944272445881</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -14558,11 +14559,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>15.13292433537832</v>
+        <v>15.432098765432102</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>16.94342605038986</v>
+        <v>16.804513054947961</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -14571,10 +14572,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="C21" s="6">
-        <v>39.722807017543914</v>
+        <v>39.461403508771923</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -14582,11 +14583,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>20.449897750511241</v>
+        <v>20.576131687242807</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>18.002390178539017</v>
+        <v>17.854795120882358</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -14597,7 +14598,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
-        <v>39.209803921568664</v>
+        <v>38.956862745098078</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -14607,7 +14608,7 @@
       </c>
       <c r="C23" s="6">
         <f>C22-$D$4</f>
-        <v>38.696800825593414</v>
+        <v>38.452321981424234</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -14617,7 +14618,7 @@
       </c>
       <c r="C24" s="6">
         <f>C23-$D$4</f>
-        <v>38.183797729618163</v>
+        <v>37.947781217750389</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -14627,7 +14628,7 @@
       </c>
       <c r="C25" s="6">
         <f>C24-$D$4</f>
-        <v>37.670794633642913</v>
+        <v>37.443240454076545</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15">
@@ -14849,15 +14850,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>47.811111111111131</v>
+        <v>47.476608187134502</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.43921568627456509</v>
+        <v>0.43384932920537267</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -14869,10 +14870,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="C5" s="6">
-        <v>47.371895424836566</v>
+        <v>47.04275885792913</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -14880,15 +14881,15 @@
       </c>
       <c r="T5" s="1">
         <f>100 - 100 * B5/$B$4</f>
-        <v>-0.8602150537634401</v>
+        <v>-0.86580086580086402</v>
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.91864772867094757</v>
+        <v>0.91381702647187524</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.9186477286707202</v>
+        <v>0.91381702647186103</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -14897,10 +14898,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="C6" s="6">
-        <v>46.932679738562115</v>
+        <v>46.608909528723757</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -14908,11 +14909,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>1.5053763440860166</v>
+        <v>1.5151515151515156</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>1.8372954573416678</v>
+        <v>1.8276340529437363</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -14921,10 +14922,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
       <c r="C7" s="6">
-        <v>46.49346405228755</v>
+        <v>46.175060199518384</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -14932,11 +14933,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
-        <v>-0.43010752688172715</v>
+        <v>-0.21645021645021245</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>2.7559431860126153</v>
+        <v>2.7414510794156115</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -14945,10 +14946,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="C8" s="6">
-        <v>46.054248366013098</v>
+        <v>45.741210870313012</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -14956,11 +14957,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>-2.5806451612903203</v>
+        <v>-2.3809523809523796</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>3.6745909146833071</v>
+        <v>3.6552681058874867</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -14969,10 +14970,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="C9" s="6">
-        <v>45.615032679738533</v>
+        <v>45.307361541107639</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -14980,11 +14981,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>1.7204301075268802</v>
+        <v>1.7316017316017422</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>4.5932386433542547</v>
+        <v>4.5690851323593478</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -14993,10 +14994,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="C10" s="6">
-        <v>45.175816993464082</v>
+        <v>44.873512211902266</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -15004,11 +15005,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>-5.1612903225806406</v>
+        <v>-4.9783549783549716</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>5.5118863720249607</v>
+        <v>5.4829021588312088</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -15017,10 +15018,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="C11" s="6">
-        <v>44.736601307189517</v>
+        <v>44.439662882696894</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -15028,11 +15029,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>6.6666666666666714</v>
+        <v>6.4935064935065014</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>6.4305341006959083</v>
+        <v>6.396719185303084</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -15041,10 +15042,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="C12" s="6">
-        <v>44.297385620915065</v>
+        <v>44.005813553491521</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -15052,11 +15053,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>2.5806451612903203</v>
+        <v>2.8138528138528187</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>7.3491818293666284</v>
+        <v>7.3105362117749593</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -15065,10 +15066,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="C13" s="6">
-        <v>43.8581699346405</v>
+        <v>43.571964224286148</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -15076,11 +15077,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>10.107526881720432</v>
+        <v>9.9567099567099575</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>8.267829558037576</v>
+        <v>8.2243532382468203</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -15089,10 +15090,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="C14" s="6">
-        <v>43.418954248366049</v>
+        <v>43.138114895080776</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -15100,11 +15101,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>5.8064516129032313</v>
+        <v>5.8441558441558499</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>9.186477286708282</v>
+        <v>9.1381702647186813</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -15113,10 +15114,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="C15" s="6">
-        <v>42.979738562091484</v>
+        <v>42.704265565875403</v>
       </c>
       <c r="S15" s="7">
         <f t="shared" si="1"/>
@@ -15124,11 +15125,11 @@
       </c>
       <c r="T15" s="8">
         <f t="shared" si="3"/>
-        <v>4.0860215053763511</v>
+        <v>3.8961038961038952</v>
       </c>
       <c r="U15" s="12">
         <f t="shared" si="2"/>
-        <v>10.10512501537923</v>
+        <v>10.051987291190571</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -15137,10 +15138,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="C16" s="6">
-        <v>42.540522875817032</v>
+        <v>42.27041623667003</v>
       </c>
       <c r="S16" s="7">
         <f t="shared" si="1"/>
@@ -15148,11 +15149,11 @@
       </c>
       <c r="T16" s="8">
         <f t="shared" si="3"/>
-        <v>11.612903225806448</v>
+        <v>11.255411255411261</v>
       </c>
       <c r="U16" s="12">
         <f t="shared" si="2"/>
-        <v>11.023772744049936</v>
+        <v>10.965804317662446</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -15161,10 +15162,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="C17" s="6">
-        <v>42.101307189542467</v>
+        <v>41.836566907464658</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -15172,11 +15173,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>10.752688172043008</v>
+        <v>10.606060606060609</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>11.942420472720883</v>
+        <v>11.879621344134307</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -15185,10 +15186,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="C18" s="6">
-        <v>41.662091503268016</v>
+        <v>41.402717578259285</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -15196,11 +15197,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>11.397849462365585</v>
+        <v>11.471861471861473</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>12.861068201391575</v>
+        <v>12.793438370606168</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -15209,10 +15210,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="C19" s="6">
-        <v>41.222875816993451</v>
+        <v>40.968868249053912</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -15220,11 +15221,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>11.397849462365585</v>
+        <v>11.471861471861473</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>13.779715930062522</v>
+        <v>13.707255397078043</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -15233,10 +15234,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>40.799999999999997</v>
+        <v>40.5</v>
       </c>
       <c r="C20" s="6">
-        <v>40.783660130718999</v>
+        <v>40.53501891984854</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -15244,11 +15245,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>12.258064516129039</v>
+        <v>12.337662337662337</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>14.698363658733243</v>
+        <v>14.621072423549919</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -15257,10 +15258,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>40.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="C21" s="6">
-        <v>40.344444444444434</v>
+        <v>40.101169590643281</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -15268,11 +15269,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>12.903225806451616</v>
+        <v>12.987012987012989</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>15.61701138740419</v>
+        <v>15.534889450021538</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -15283,7 +15284,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
-        <v>39.905228758169869</v>
+        <v>39.667320261437908</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -15293,7 +15294,7 @@
       </c>
       <c r="C23" s="6">
         <f t="shared" ref="C23:C25" si="4">C22-$D$4</f>
-        <v>39.466013071895304</v>
+        <v>39.233470932232535</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -15303,7 +15304,7 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" si="4"/>
-        <v>39.026797385620739</v>
+        <v>38.799621603027163</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -15313,7 +15314,7 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="4"/>
-        <v>38.587581699346174</v>
+        <v>38.36577227382179</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="15">
@@ -15534,15 +15535,15 @@
         <v>1896</v>
       </c>
       <c r="B4" s="5">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="C4" s="6" cm="1">
         <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>46.139181286549729</v>
+        <v>45.785380116959004</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.45036119711051015</v>
+        <v>0.44272445820433859</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
@@ -15554,10 +15555,10 @@
         <v>1897</v>
       </c>
       <c r="B5" s="5">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="C5" s="6">
-        <v>45.688820089439218</v>
+        <v>45.342655658754666</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -15569,11 +15570,11 @@
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.97609273626578386</v>
+        <v>0.96695595203838991</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.97609273626552806</v>
+        <v>0.96695595203840412</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -15582,10 +15583,10 @@
         <v>1898</v>
       </c>
       <c r="B6" s="5">
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
       <c r="C6" s="6">
-        <v>45.238458892328822</v>
+        <v>44.899931200550327</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -15593,11 +15594,11 @@
       </c>
       <c r="T6" s="1">
         <f>100 - 100 * B6/$B$4</f>
-        <v>2.2172949002217308</v>
+        <v>2.4553571428571388</v>
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>1.9521854725313119</v>
+        <v>1.933911904076794</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -15606,10 +15607,10 @@
         <v>1899</v>
       </c>
       <c r="B7" s="5">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="C7" s="6">
-        <v>44.788097695218426</v>
+        <v>44.457206742345988</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -15617,11 +15618,11 @@
       </c>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T21" si="3">100 - 100 * B7/$B$4</f>
-        <v>0.22172949002217024</v>
+        <v>0.4464285714285694</v>
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>2.92827820879684</v>
+        <v>2.9008678561151839</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -15630,10 +15631,10 @@
         <v>1900</v>
       </c>
       <c r="B8" s="5">
-        <v>46.1</v>
+        <v>45.8</v>
       </c>
       <c r="C8" s="6">
-        <v>44.337736498108029</v>
+        <v>44.01448228414165</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -15641,11 +15642,11 @@
       </c>
       <c r="T8" s="1">
         <f t="shared" si="3"/>
-        <v>-2.2172949002217308</v>
+        <v>-2.2321428571428612</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>3.904370945062368</v>
+        <v>3.8678238081535739</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -15654,10 +15655,10 @@
         <v>1901</v>
       </c>
       <c r="B9" s="5">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="C9" s="6">
-        <v>43.887375300997633</v>
+        <v>43.571757825937311</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -15665,11 +15666,11 @@
       </c>
       <c r="T9" s="1">
         <f t="shared" si="3"/>
-        <v>2.4390243902439011</v>
+        <v>2.4553571428571388</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>4.8804636813279103</v>
+        <v>4.834779760191978</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -15678,10 +15679,10 @@
         <v>1902</v>
       </c>
       <c r="B10" s="5">
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
       <c r="C10" s="6">
-        <v>43.437014103887122</v>
+        <v>43.129033367732973</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -15689,11 +15690,11 @@
       </c>
       <c r="T10" s="1">
         <f t="shared" si="3"/>
-        <v>-3.7694013303769367</v>
+        <v>-3.3482142857142918</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>5.8565564175936657</v>
+        <v>5.8017357122303679</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -15702,10 +15703,10 @@
         <v>1903</v>
       </c>
       <c r="B11" s="5">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="C11" s="6">
-        <v>42.986652906776726</v>
+        <v>42.686308909528634</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -15713,11 +15714,11 @@
       </c>
       <c r="T11" s="1">
         <f t="shared" si="3"/>
-        <v>7.3170731707317032</v>
+        <v>7.1428571428571388</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>6.8326491538591938</v>
+        <v>6.7686916642687578</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -15726,10 +15727,10 @@
         <v>1904</v>
       </c>
       <c r="B12" s="5">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="C12" s="6">
-        <v>42.53629170966633</v>
+        <v>42.243584451324409</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -15737,11 +15738,11 @@
       </c>
       <c r="T12" s="1">
         <f t="shared" si="3"/>
-        <v>4.6563192904656319</v>
+        <v>4.9107142857142776</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>7.8087418901247361</v>
+        <v>7.7356476163069203</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -15750,10 +15751,10 @@
         <v>1905</v>
       </c>
       <c r="B13" s="5">
-        <v>40.4</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="C13" s="6">
-        <v>42.085930512555933</v>
+        <v>41.800859993120071</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -15761,11 +15762,11 @@
       </c>
       <c r="T13" s="1">
         <f t="shared" si="3"/>
-        <v>10.421286031042129</v>
+        <v>10.267857142857125</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>8.7848346263902641</v>
+        <v>8.7026035683453102</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -15774,10 +15775,10 @@
         <v>1906</v>
       </c>
       <c r="B14" s="5">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="C14" s="6">
-        <v>41.635569315445423</v>
+        <v>41.358135534915732</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -15785,11 +15786,11 @@
       </c>
       <c r="T14" s="1">
         <f t="shared" si="3"/>
-        <v>7.9822616407982281</v>
+        <v>8.0357142857142776</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>9.7609273626560196</v>
+        <v>9.6695595203837001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -15798,10 +15799,10 @@
         <v>1907</v>
       </c>
       <c r="B15" s="5">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="C15" s="6">
-        <v>41.185208118335026</v>
+        <v>40.915411076711393</v>
       </c>
       <c r="S15" s="7">
         <f t="shared" si="1"/>
@@ -15809,11 +15810,11 @@
       </c>
       <c r="T15" s="8">
         <f t="shared" si="3"/>
-        <v>5.0997782705099866</v>
+        <v>4.9107142857142776</v>
       </c>
       <c r="U15" s="12">
         <f t="shared" si="2"/>
-        <v>10.737020098921562</v>
+        <v>10.63651547242209</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -15822,10 +15823,10 @@
         <v>1908</v>
       </c>
       <c r="B16" s="5">
-        <v>39.700000000000003</v>
+        <v>39.6</v>
       </c>
       <c r="C16" s="6">
-        <v>40.73484692122463</v>
+        <v>40.472686618507055</v>
       </c>
       <c r="S16" s="7">
         <f t="shared" si="1"/>
@@ -15833,11 +15834,11 @@
       </c>
       <c r="T16" s="8">
         <f t="shared" si="3"/>
-        <v>11.973392461197335</v>
+        <v>11.607142857142847</v>
       </c>
       <c r="U16" s="12">
         <f t="shared" si="2"/>
-        <v>11.71311283518709</v>
+        <v>11.60347142446048</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -15846,10 +15847,10 @@
         <v>1909</v>
       </c>
       <c r="B17" s="5">
-        <v>39.9</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="C17" s="6">
-        <v>40.284485724114234</v>
+        <v>40.029962160302716</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -15857,11 +15858,11 @@
       </c>
       <c r="T17" s="1">
         <f t="shared" si="3"/>
-        <v>11.529933481152995</v>
+        <v>11.383928571428555</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>12.689205571452618</v>
+        <v>12.57042737649887</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -15870,10 +15871,10 @@
         <v>1910</v>
       </c>
       <c r="B18" s="5">
-        <v>39.5</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="C18" s="6">
-        <v>39.834124527003723</v>
+        <v>39.587237702098378</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -15881,11 +15882,11 @@
       </c>
       <c r="T18" s="1">
         <f t="shared" si="3"/>
-        <v>12.41685144124169</v>
+        <v>12.276785714285722</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>13.665298307718402</v>
+        <v>13.537383328537274</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -15894,10 +15895,10 @@
         <v>1911</v>
       </c>
       <c r="B19" s="5">
-        <v>39.299999999999997</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>39.383763329893327</v>
+        <v>39.144513243894039</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -15905,11 +15906,11 @@
       </c>
       <c r="T19" s="1">
         <f t="shared" si="3"/>
-        <v>12.860310421286044</v>
+        <v>12.946428571428569</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>14.64139104398393</v>
+        <v>14.504339280575664</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -15918,10 +15919,10 @@
         <v>1912</v>
       </c>
       <c r="B20" s="5">
-        <v>39.200000000000003</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="C20" s="6">
-        <v>38.93340213278293</v>
+        <v>38.7017887856897</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -15929,11 +15930,11 @@
       </c>
       <c r="T20" s="1">
         <f t="shared" si="3"/>
-        <v>13.0820399113082</v>
+        <v>13.392857142857153</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>15.617483780249458</v>
+        <v>15.471295232614054</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -15942,10 +15943,10 @@
         <v>1913</v>
       </c>
       <c r="B21" s="5">
-        <v>38.299999999999997</v>
+        <v>38.1</v>
       </c>
       <c r="C21" s="6">
-        <v>38.483040935672534</v>
+        <v>38.259064327485362</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -15953,11 +15954,11 @@
       </c>
       <c r="T21" s="1">
         <f t="shared" si="3"/>
-        <v>15.077605321507775</v>
+        <v>14.955357142857139</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>16.593576516514986</v>
+        <v>16.438251184652458</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -15968,7 +15969,7 @@
       <c r="B22" s="1"/>
       <c r="C22" s="6">
         <f>C21-$D$4</f>
-        <v>38.032679738562024</v>
+        <v>37.816339869281023</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -15978,7 +15979,7 @@
       </c>
       <c r="C23" s="6">
         <f t="shared" ref="C23:C25" si="4">C22-$D$4</f>
-        <v>37.582318541451514</v>
+        <v>37.373615411076685</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -15988,7 +15989,7 @@
       </c>
       <c r="C24" s="6">
         <f t="shared" si="4"/>
-        <v>37.131957344341004</v>
+        <v>36.930890952872346</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -15998,7 +15999,7 @@
       </c>
       <c r="C25" s="6">
         <f t="shared" si="4"/>
-        <v>36.681596147230493</v>
+        <v>36.488166494668008</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="15">
@@ -16211,23 +16212,23 @@
       </c>
       <c r="B4" s="5">
         <f>RSFSR!B4</f>
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="C4" s="5">
         <f>NR!B4</f>
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="D4" s="5">
         <f>MR!B4</f>
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="E4" s="5">
         <f>F4</f>
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="F4">
         <f>'BR без Смоленской'!B4</f>
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -16237,23 +16238,23 @@
       </c>
       <c r="B5" s="5">
         <f>RSFSR!B5</f>
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
       <c r="C5" s="5">
         <f>NR!B5</f>
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="D5" s="5">
         <f>MR!B5</f>
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5">
         <f>BR!B5</f>
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="F5" s="1">
         <f>'BR без Смоленской'!B5</f>
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -16263,23 +16264,23 @@
       </c>
       <c r="B6" s="5">
         <f>RSFSR!B6</f>
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="C6" s="5">
         <f>NR!B6</f>
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="D6" s="5">
         <f>MR!B6</f>
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="E6" s="5">
         <f>BR!B6</f>
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="F6" s="1">
         <f>'BR без Смоленской'!B6</f>
-        <v>44.1</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -16289,23 +16290,23 @@
       </c>
       <c r="B7" s="5">
         <f>RSFSR!B7</f>
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="C7" s="5">
         <f>NR!B7</f>
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="D7" s="5">
         <f>MR!B7</f>
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
       <c r="E7" s="5">
         <f>BR!B7</f>
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
       <c r="F7" s="1">
         <f>'BR без Смоленской'!B7</f>
-        <v>45</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -16315,23 +16316,23 @@
       </c>
       <c r="B8" s="5">
         <f>RSFSR!B8</f>
-        <v>52.4</v>
+        <v>51.9</v>
       </c>
       <c r="C8" s="5">
         <f>NR!B8</f>
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="D8" s="5">
         <f>MR!B8</f>
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E8" s="5">
         <f>BR!B8</f>
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="F8" s="1">
         <f>'BR без Смоленской'!B8</f>
-        <v>46.1</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -16341,23 +16342,23 @@
       </c>
       <c r="B9" s="5">
         <f>RSFSR!B9</f>
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="C9" s="5">
         <f>NR!B9</f>
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
       <c r="D9" s="5">
         <f>MR!B9</f>
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="E9" s="5">
         <f>BR!B9</f>
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="F9" s="1">
         <f>'BR без Смоленской'!B9</f>
-        <v>44</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -16367,23 +16368,23 @@
       </c>
       <c r="B10" s="5">
         <f>RSFSR!B10</f>
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="C10" s="5">
         <f>NR!B10</f>
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="D10" s="5">
         <f>MR!B10</f>
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="E10" s="5">
         <f>BR!B10</f>
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F10" s="1">
         <f>'BR без Смоленской'!B10</f>
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -16393,23 +16394,23 @@
       </c>
       <c r="B11" s="5">
         <f>RSFSR!B11</f>
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5">
         <f>NR!B11</f>
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="D11" s="5">
         <f>MR!B11</f>
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
       <c r="E11" s="5">
         <f>BR!B11</f>
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="F11" s="1">
         <f>'BR без Смоленской'!B11</f>
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16419,23 +16420,23 @@
       </c>
       <c r="B12" s="5">
         <f>RSFSR!B12</f>
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="C12" s="5">
         <f>NR!B12</f>
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="D12" s="5">
         <f>MR!B12</f>
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
       <c r="E12" s="5">
         <f>BR!B12</f>
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="F12" s="1">
         <f>'BR без Смоленской'!B12</f>
-        <v>43</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -16445,23 +16446,23 @@
       </c>
       <c r="B13" s="5">
         <f>RSFSR!B13</f>
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="C13" s="5">
         <f>NR!B13</f>
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="D13" s="5">
         <f>MR!B13</f>
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="E13" s="5">
         <f>BR!B13</f>
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="F13" s="1">
         <f>'BR без Смоленской'!B13</f>
-        <v>40.4</v>
+        <v>40.200000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -16471,23 +16472,23 @@
       </c>
       <c r="B14" s="5">
         <f>RSFSR!B14</f>
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="C14" s="5">
         <f>NR!B14</f>
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="D14" s="5">
         <f>MR!B14</f>
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="E14" s="5">
         <f>BR!B14</f>
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="F14" s="1">
         <f>'BR без Смоленской'!B14</f>
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -16497,23 +16498,23 @@
       </c>
       <c r="B15" s="5">
         <f>RSFSR!B15</f>
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="C15" s="5">
         <f>NR!B15</f>
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="D15" s="5">
         <f>MR!B15</f>
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="E15" s="5">
         <f>BR!B15</f>
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="F15" s="1">
         <f>'BR без Смоленской'!B15</f>
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16523,23 +16524,23 @@
       </c>
       <c r="B16" s="5">
         <f>RSFSR!B16</f>
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="C16" s="5">
         <f>NR!B16</f>
-        <v>47.6</v>
+        <v>47.2</v>
       </c>
       <c r="D16" s="5">
         <f>MR!B16</f>
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="E16" s="5">
         <f>BR!B16</f>
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1">
         <f>'BR без Смоленской'!B16</f>
-        <v>39.700000000000003</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -16549,23 +16550,23 @@
       </c>
       <c r="B17" s="5">
         <f>RSFSR!B17</f>
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="C17" s="5">
         <f>NR!B17</f>
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="D17" s="5">
         <f>MR!B17</f>
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5">
         <f>BR!B17</f>
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="F17" s="1">
         <f>'BR без Смоленской'!B17</f>
-        <v>39.9</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -16575,23 +16576,23 @@
       </c>
       <c r="B18" s="5">
         <f>RSFSR!B18</f>
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="C18" s="5">
         <f>NR!B18</f>
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="D18" s="5">
         <f>MR!B18</f>
-        <v>40.9</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="E18" s="5">
         <f>BR!B18</f>
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="F18" s="1">
         <f>'BR без Смоленской'!B18</f>
-        <v>39.5</v>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16601,23 +16602,23 @@
       </c>
       <c r="B19" s="5">
         <f>RSFSR!B19</f>
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="C19" s="5">
         <f>NR!B19</f>
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
       <c r="D19" s="5">
         <f>MR!B19</f>
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="E19" s="5">
         <f>BR!B19</f>
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="F19" s="1">
         <f>'BR без Смоленской'!B19</f>
-        <v>39.299999999999997</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16627,23 +16628,23 @@
       </c>
       <c r="B20" s="5">
         <f>RSFSR!B20</f>
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="C20" s="5">
         <f>NR!B20</f>
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
       <c r="D20" s="5">
         <f>MR!B20</f>
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="E20" s="5">
         <f>BR!B20</f>
-        <v>40.799999999999997</v>
+        <v>40.5</v>
       </c>
       <c r="F20" s="1">
         <f>'BR без Смоленской'!B20</f>
-        <v>39.200000000000003</v>
+        <v>38.799999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16653,23 +16654,23 @@
       </c>
       <c r="B21" s="5">
         <f>RSFSR!B21</f>
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="C21" s="5">
         <f>NR!B21</f>
-        <v>46.5</v>
+        <v>46.1</v>
       </c>
       <c r="D21" s="5">
         <f>MR!B21</f>
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="E21" s="5">
         <f>BR!B21</f>
-        <v>40.5</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="F21" s="1">
         <f>'BR без Смоленской'!B21</f>
-        <v>38.299999999999997</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16678,11 +16679,11 @@
       </c>
       <c r="B22" s="5">
         <f>RSFSR!B22</f>
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="C22" s="5">
         <f>NR!B22</f>
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/start-of-demographic-transition-ru.xlsx
+++ b/workbooks/start-of-demographic-transition-ru.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E38DDC-6160-4653-84F9-1670E7D39443}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068D6203-2C0D-47F3-A859-931A7F0C895F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="750" windowWidth="25635" windowHeight="21885" activeTab="1" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
+    <workbookView xWindow="16605" yWindow="960" windowWidth="20115" windowHeight="21600" activeTab="2" xr2:uid="{4FC66C36-D870-40C8-814E-E325D68632DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="STEP_NR">NR!$V$5</definedName>
     <definedName name="STEP_RSFSR">RSFSR!$V$5</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,14 +48,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -189,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -278,6 +283,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2162,6 +2168,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2169,7 +2176,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3346,6 +3352,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3353,7 +3360,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12401,114 +12407,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA223DA1-90A1-4FE4-821C-7E7F6AA5A7D6}">
   <dimension ref="A2:B32"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:2" ht="15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>24</v>
       </c>
@@ -12521,21 +12527,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14800EA2-8841-4A8E-9FAD-F1492223CF40}">
   <dimension ref="A1:V60"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="20" max="20" width="25.375" customWidth="1"/>
-    <col min="21" max="21" width="26.375" customWidth="1"/>
-    <col min="22" max="22" width="21.75" customWidth="1"/>
+    <col min="20" max="20" width="25.42578125" customWidth="1"/>
+    <col min="21" max="21" width="26.42578125" customWidth="1"/>
+    <col min="22" max="22" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -12561,7 +12567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -12580,7 +12586,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -12608,7 +12614,7 @@
         <v>0.40746700783277845</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -12632,7 +12638,7 @@
         <v>0.8149340156656848</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -12656,7 +12662,7 @@
         <v>1.2224010234984917</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -12680,7 +12686,7 @@
         <v>1.6298680313313838</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -12704,7 +12710,7 @@
         <v>2.0373350391641765</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -12728,7 +12734,7 @@
         <v>2.4448020469969833</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -12752,7 +12758,7 @@
         <v>2.852269054829776</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -12776,7 +12782,7 @@
         <v>3.2597360626626681</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -12800,7 +12806,7 @@
         <v>3.667203070495475</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -12824,7 +12830,7 @@
         <v>4.0746700783282535</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -12848,7 +12854,7 @@
         <v>4.4821370861611456</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -12872,7 +12878,7 @@
         <v>4.8896040939939525</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -12896,7 +12902,7 @@
         <v>5.2970711018267451</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -12920,7 +12926,7 @@
         <v>5.7045381096596373</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -12944,7 +12950,7 @@
         <v>6.1120051174924441</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -12968,7 +12974,7 @@
         <v>6.5194721253252368</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -12992,7 +12998,7 @@
         <v>6.9269391331581289</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>1914</v>
       </c>
@@ -13014,7 +13020,7 @@
         <v>7.3344061409909358</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" ref="A23:A29" si="4">A22+1</f>
         <v>1915</v>
@@ -13029,10 +13035,10 @@
       </c>
       <c r="U23" s="6">
         <f t="shared" ref="U23:U35" si="5">U22+STEP</f>
-        <v>7.7856853439623848</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
+        <v>7.8534079701180559</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="4"/>
         <v>1916</v>
@@ -13047,10 +13053,10 @@
       </c>
       <c r="U24" s="6">
         <f t="shared" si="5"/>
-        <v>8.2369645469338337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
+        <v>8.372409799245176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="4"/>
         <v>1917</v>
@@ -13065,10 +13071,10 @@
       </c>
       <c r="U25" s="6">
         <f t="shared" si="5"/>
-        <v>8.6882437499052827</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
+        <v>8.8914116283722961</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" si="4"/>
         <v>1918</v>
@@ -13083,10 +13089,10 @@
       </c>
       <c r="U26" s="6">
         <f t="shared" si="5"/>
-        <v>9.1395229528767317</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
+        <v>9.4104134574994163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="4"/>
         <v>1919</v>
@@ -13101,10 +13107,10 @@
       </c>
       <c r="U27" s="6">
         <f t="shared" si="5"/>
-        <v>9.5908021558481806</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
+        <v>9.9294152866265364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f t="shared" si="4"/>
         <v>1920</v>
@@ -13119,10 +13125,10 @@
       </c>
       <c r="U28" s="12">
         <f t="shared" si="5"/>
-        <v>10.04208135881963</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
+        <v>10.448417115753657</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <f t="shared" si="4"/>
         <v>1921</v>
@@ -13138,75 +13144,75 @@
       <c r="T29" s="9"/>
       <c r="U29" s="12">
         <f t="shared" si="5"/>
-        <v>10.493360561791079</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21">
+        <v>10.967418944880777</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S30" s="4">
         <f t="shared" si="7"/>
         <v>1922</v>
       </c>
       <c r="U30" s="6">
         <f t="shared" si="5"/>
-        <v>10.944639764762528</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
+        <v>11.486420774007897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S31" s="4">
         <f t="shared" si="7"/>
         <v>1923</v>
       </c>
       <c r="U31" s="6">
         <f t="shared" si="5"/>
-        <v>11.395918967733977</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21">
+        <v>12.005422603135017</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S32" s="4">
         <f t="shared" si="7"/>
         <v>1924</v>
       </c>
       <c r="U32" s="6">
         <f t="shared" si="5"/>
-        <v>11.847198170705425</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21">
+        <v>12.524424432262137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S33" s="4">
         <f t="shared" si="7"/>
         <v>1925</v>
       </c>
       <c r="U33" s="6">
         <f t="shared" si="5"/>
-        <v>12.298477373676874</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
+        <v>13.043426261389257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S34" s="4">
         <f t="shared" si="7"/>
         <v>1926</v>
       </c>
       <c r="U34" s="6">
         <f t="shared" si="5"/>
-        <v>12.749756576648323</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+        <v>13.562428090516377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="S35" s="4">
         <f t="shared" si="7"/>
         <v>1927</v>
       </c>
       <c r="U35" s="6">
         <f t="shared" si="5"/>
-        <v>13.201035779619772</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15">
+        <v>14.081429919643497</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="15">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>0</v>
       </c>
@@ -13214,7 +13220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>1896</v>
       </c>
@@ -13222,7 +13228,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f>A42+1</f>
         <v>1897</v>
@@ -13231,14 +13237,14 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" ref="A44:A59" si="8">A43+1</f>
         <v>1898</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f t="shared" si="8"/>
         <v>1899</v>
@@ -13247,7 +13253,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f t="shared" si="8"/>
         <v>1900</v>
@@ -13256,7 +13262,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f t="shared" si="8"/>
         <v>1901</v>
@@ -13265,7 +13271,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f t="shared" si="8"/>
         <v>1902</v>
@@ -13274,7 +13280,7 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <f t="shared" si="8"/>
         <v>1903</v>
@@ -13283,7 +13289,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <f t="shared" si="8"/>
         <v>1904</v>
@@ -13292,14 +13298,14 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <f t="shared" si="8"/>
         <v>1905</v>
       </c>
       <c r="B51" s="5"/>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <f t="shared" si="8"/>
         <v>1906</v>
@@ -13308,7 +13314,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <f t="shared" si="8"/>
         <v>1907</v>
@@ -13317,28 +13323,28 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <f t="shared" si="8"/>
         <v>1908</v>
       </c>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <f t="shared" si="8"/>
         <v>1909</v>
       </c>
       <c r="B55" s="5"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <f t="shared" si="8"/>
         <v>1910</v>
       </c>
       <c r="B56" s="5"/>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <f t="shared" si="8"/>
         <v>1911</v>
@@ -13347,7 +13353,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <f t="shared" si="8"/>
         <v>1912</v>
@@ -13356,7 +13362,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <f t="shared" si="8"/>
         <v>1913</v>
@@ -13365,7 +13371,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>1914</v>
       </c>
@@ -13383,21 +13389,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F786236-6DB6-44ED-BB49-A78B092F8D0C}">
   <dimension ref="A1:V50"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="20" max="20" width="25" customWidth="1"/>
     <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="23.25" customWidth="1"/>
+    <col min="22" max="22" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -13423,7 +13429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -13431,18 +13437,18 @@
         <v>51.5</v>
       </c>
       <c r="C4" s="6" cm="1">
-        <f t="array" ref="C4:C21">TREND($B$4:$B$21,$A$4:$A$21,A4:A21)</f>
-        <v>50.538596491228134</v>
+        <f t="array" ref="C4:C22">TREND($B$4:$B$22,$A$4:$A$22,A4:A22)</f>
+        <v>50.738421052631566</v>
       </c>
       <c r="D4" s="6">
         <f>C4-C5</f>
-        <v>0.2280701754386314</v>
+        <v>0.26333333333332121</v>
       </c>
       <c r="S4" s="4">
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -13451,7 +13457,7 @@
         <v>50.9</v>
       </c>
       <c r="C5" s="6">
-        <v>50.310526315789502</v>
+        <v>50.475087719298244</v>
       </c>
       <c r="S5" s="4">
         <f>S4+1</f>
@@ -13463,14 +13469,14 @@
       </c>
       <c r="U5" s="6">
         <f>100 - 100 * C5/$C$4</f>
-        <v>0.45127920297156265</v>
+        <v>0.51900182912700643</v>
       </c>
       <c r="V5" s="6">
         <f>U6-U5</f>
-        <v>0.45127920297144897</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+        <v>0.51900182912712012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -13479,7 +13485,7 @@
         <v>49.9</v>
       </c>
       <c r="C6" s="6">
-        <v>50.082456140350928</v>
+        <v>50.211754385964866</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" ref="S6:S21" si="1">S5+1</f>
@@ -13491,10 +13497,10 @@
       </c>
       <c r="U6" s="6">
         <f t="shared" ref="U6:U21" si="2">100 - 100 * C6/$C$4</f>
-        <v>0.90255840594301162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <v>1.0380036582541265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -13503,7 +13509,7 @@
         <v>50.6</v>
       </c>
       <c r="C7" s="6">
-        <v>49.854385964912353</v>
+        <v>49.948421052631545</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="1"/>
@@ -13515,10 +13521,10 @@
       </c>
       <c r="U7" s="6">
         <f t="shared" si="2"/>
-        <v>1.3538376089144748</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <v>1.557005487381133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -13527,7 +13533,7 @@
         <v>49.8</v>
       </c>
       <c r="C8" s="6">
-        <v>49.626315789473722</v>
+        <v>49.685087719298224</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="1"/>
@@ -13539,10 +13545,10 @@
       </c>
       <c r="U8" s="6">
         <f t="shared" si="2"/>
-        <v>1.8051168118860517</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+        <v>2.0760073165081394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -13551,7 +13557,7 @@
         <v>46.3</v>
       </c>
       <c r="C9" s="6">
-        <v>49.398245614035147</v>
+        <v>49.421754385964903</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="1"/>
@@ -13563,10 +13569,10 @@
       </c>
       <c r="U9" s="6">
         <f t="shared" si="2"/>
-        <v>2.2563960148575006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+        <v>2.5950091456351458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -13575,7 +13581,7 @@
         <v>49.9</v>
       </c>
       <c r="C10" s="6">
-        <v>49.170175438596516</v>
+        <v>49.158421052631581</v>
       </c>
       <c r="S10" s="4">
         <f t="shared" si="1"/>
@@ -13587,10 +13593,10 @@
       </c>
       <c r="U10" s="6">
         <f t="shared" si="2"/>
-        <v>2.7076752178290775</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
+        <v>3.1140109747621665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -13599,7 +13605,7 @@
         <v>49.5</v>
       </c>
       <c r="C11" s="6">
-        <v>48.942105263157941</v>
+        <v>48.895087719298203</v>
       </c>
       <c r="S11" s="4">
         <f t="shared" si="1"/>
@@ -13611,10 +13617,10 @@
       </c>
       <c r="U11" s="6">
         <f t="shared" si="2"/>
-        <v>3.1589544208005407</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+        <v>3.6330128038892724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -13623,7 +13629,7 @@
         <v>49.6</v>
       </c>
       <c r="C12" s="6">
-        <v>48.714035087719367</v>
+        <v>48.631754385964882</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="1"/>
@@ -13635,10 +13641,10 @@
       </c>
       <c r="U12" s="6">
         <f t="shared" si="2"/>
-        <v>3.6102336237719896</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>4.152014633016293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -13647,7 +13653,7 @@
         <v>45.6</v>
       </c>
       <c r="C13" s="6">
-        <v>48.485964912280735</v>
+        <v>48.368421052631561</v>
       </c>
       <c r="S13" s="4">
         <f t="shared" si="1"/>
@@ -13659,10 +13665,10 @@
       </c>
       <c r="U13" s="6">
         <f t="shared" si="2"/>
-        <v>4.0615128267435523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+        <v>4.6710164621432995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -13671,7 +13677,7 @@
         <v>46.6</v>
       </c>
       <c r="C14" s="6">
-        <v>48.257894736842161</v>
+        <v>48.10508771929824</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="1"/>
@@ -13683,10 +13689,10 @@
       </c>
       <c r="U14" s="6">
         <f t="shared" si="2"/>
-        <v>4.5127920297150013</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+        <v>5.1900182912703059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -13695,7 +13701,7 @@
         <v>49.8</v>
       </c>
       <c r="C15" s="6">
-        <v>48.029824561403586</v>
+        <v>47.841754385964919</v>
       </c>
       <c r="S15" s="4">
         <f t="shared" si="1"/>
@@ -13707,10 +13713,10 @@
       </c>
       <c r="U15" s="6">
         <f t="shared" si="2"/>
-        <v>4.9640712326864644</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+        <v>5.7090201203973123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -13719,7 +13725,7 @@
         <v>47.2</v>
       </c>
       <c r="C16" s="6">
-        <v>47.801754385964955</v>
+        <v>47.578421052631541</v>
       </c>
       <c r="S16" s="4">
         <f t="shared" si="1"/>
@@ -13731,10 +13737,10 @@
       </c>
       <c r="U16" s="6">
         <f t="shared" si="2"/>
-        <v>5.4153504356580271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21">
+        <v>6.2280219495244467</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -13743,7 +13749,7 @@
         <v>48.5</v>
       </c>
       <c r="C17" s="6">
-        <v>47.57368421052638</v>
+        <v>47.315087719298219</v>
       </c>
       <c r="S17" s="4">
         <f t="shared" si="1"/>
@@ -13755,10 +13761,10 @@
       </c>
       <c r="U17" s="6">
         <f t="shared" si="2"/>
-        <v>5.8666296386294903</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
+        <v>6.7470237786514531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -13767,7 +13773,7 @@
         <v>47.8</v>
       </c>
       <c r="C18" s="6">
-        <v>47.345614035087749</v>
+        <v>47.051754385964898</v>
       </c>
       <c r="S18" s="4">
         <f t="shared" si="1"/>
@@ -13779,10 +13785,10 @@
       </c>
       <c r="U18" s="6">
         <f t="shared" si="2"/>
-        <v>6.3179088416010671</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
+        <v>7.2660256077784595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -13791,7 +13797,7 @@
         <v>47.8</v>
       </c>
       <c r="C19" s="6">
-        <v>47.117543859649174</v>
+        <v>46.788421052631577</v>
       </c>
       <c r="S19" s="4">
         <f t="shared" si="1"/>
@@ -13803,10 +13809,10 @@
       </c>
       <c r="U19" s="6">
         <f t="shared" si="2"/>
-        <v>6.7691880445725161</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21">
+        <v>7.7850274369054802</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -13815,7 +13821,7 @@
         <v>47.4</v>
       </c>
       <c r="C20" s="6">
-        <v>46.8894736842106</v>
+        <v>46.525087719298256</v>
       </c>
       <c r="S20" s="4">
         <f t="shared" si="1"/>
@@ -13827,10 +13833,10 @@
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>7.2204672475439793</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
+        <v>8.3040292660324866</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -13839,7 +13845,7 @@
         <v>46.1</v>
       </c>
       <c r="C21" s="6">
-        <v>46.661403508771969</v>
+        <v>46.261754385964878</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="1"/>
@@ -13851,10 +13857,10 @@
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>7.6717464505155419</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
+        <v>8.8230310951596067</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -13863,8 +13869,7 @@
         <v>44.2</v>
       </c>
       <c r="C22" s="6">
-        <f>C21-$D$4</f>
-        <v>46.433333333333337</v>
+        <v>45.998421052631556</v>
       </c>
       <c r="S22" s="4">
         <v>1914</v>
@@ -13872,76 +13877,76 @@
       <c r="T22" s="1"/>
       <c r="U22" s="6">
         <f>U21+STEP_NR</f>
-        <v>8.1230256534869909</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
+        <v>9.3420329242867268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:C26" si="4">C22-$D$4</f>
-        <v>46.205263157894706</v>
+        <f>C22-$D$4</f>
+        <v>45.735087719298235</v>
       </c>
       <c r="S23" s="4">
         <v>1915</v>
       </c>
-      <c r="U23" s="6">
+      <c r="U23" s="12">
         <f>U22+STEP_NR</f>
-        <v>8.5743048564584399</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
+        <v>9.8610347534138469</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
       </c>
       <c r="C24" s="6">
-        <f t="shared" si="4"/>
-        <v>45.977192982456074</v>
+        <f t="shared" ref="C24:C26" si="4">C23-$D$4</f>
+        <v>45.471754385964914</v>
       </c>
       <c r="S24" s="4">
         <v>1916</v>
       </c>
-      <c r="U24" s="6">
+      <c r="U24" s="12">
         <f>U23+STEP_NR</f>
-        <v>9.0255840594298888</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
+        <v>10.380036582540967</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
       </c>
       <c r="C25" s="6">
         <f t="shared" si="4"/>
-        <v>45.749122807017443</v>
+        <v>45.208421052631593</v>
       </c>
       <c r="S25" s="4">
         <v>1917</v>
       </c>
-      <c r="U25" s="12">
+      <c r="U25" s="16">
         <f>U24+STEP_NR</f>
-        <v>9.4768632624013378</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
+        <v>10.899038411668087</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f>A25+1</f>
         <v>1918</v>
       </c>
       <c r="C26" s="6">
         <f t="shared" si="4"/>
-        <v>45.521052631578812</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="15">
+        <v>44.945087719298272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="15">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -13949,7 +13954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>1896</v>
       </c>
@@ -13957,7 +13962,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f>A32+1</f>
         <v>1897</v>
@@ -13966,14 +13971,14 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" ref="A34:A50" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f t="shared" si="5"/>
         <v>1899</v>
@@ -13982,7 +13987,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f t="shared" si="5"/>
         <v>1900</v>
@@ -13991,7 +13996,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="5"/>
         <v>1901</v>
@@ -14000,7 +14005,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f t="shared" si="5"/>
         <v>1902</v>
@@ -14009,7 +14014,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f t="shared" si="5"/>
         <v>1903</v>
@@ -14018,7 +14023,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f t="shared" si="5"/>
         <v>1904</v>
@@ -14027,14 +14032,14 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="5"/>
         <v>1905</v>
       </c>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="5"/>
         <v>1906</v>
@@ -14043,7 +14048,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f t="shared" si="5"/>
         <v>1907</v>
@@ -14052,28 +14057,28 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" si="5"/>
         <v>1908</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f t="shared" si="5"/>
         <v>1909</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f t="shared" si="5"/>
         <v>1910</v>
       </c>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f t="shared" si="5"/>
         <v>1911</v>
@@ -14082,7 +14087,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f t="shared" si="5"/>
         <v>1912</v>
@@ -14091,7 +14096,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <f t="shared" si="5"/>
         <v>1913</v>
@@ -14100,7 +14105,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <f t="shared" si="5"/>
         <v>1914</v>
@@ -14118,22 +14123,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1AEA7-EBD2-458F-AB27-099CC8F05D58}">
   <dimension ref="A1:V48"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="2" max="2" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="10.375" customWidth="1"/>
-    <col min="20" max="20" width="24.625" customWidth="1"/>
-    <col min="21" max="21" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="20" max="20" width="24.5703125" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" customWidth="1"/>
     <col min="22" max="22" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -14159,7 +14164,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -14178,7 +14183,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -14206,7 +14211,7 @@
         <v>1.0502820659343968</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -14230,7 +14235,7 @@
         <v>2.100564131868552</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -14254,7 +14259,7 @@
         <v>3.1508461978027071</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -14278,7 +14283,7 @@
         <v>4.2011282637368765</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -14302,7 +14307,7 @@
         <v>5.2514103296712733</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -14326,7 +14331,7 @@
         <v>6.3016923956054427</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -14350,7 +14355,7 @@
         <v>7.3519744615398253</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -14374,7 +14379,7 @@
         <v>8.4022565274739804</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -14398,7 +14403,7 @@
         <v>9.4525385934081356</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -14422,7 +14427,7 @@
         <v>10.502820659342532</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -14446,7 +14451,7 @@
         <v>11.553102725276688</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -14470,7 +14475,7 @@
         <v>12.603384791211084</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -14494,7 +14499,7 @@
         <v>13.653666857145254</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -14518,7 +14523,7 @@
         <v>14.703948923079409</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -14542,7 +14547,7 @@
         <v>15.754230989013806</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -14566,7 +14571,7 @@
         <v>16.804513054947961</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -14590,7 +14595,7 @@
         <v>17.854795120882358</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -14601,7 +14606,7 @@
         <v>38.956862745098078</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -14611,7 +14616,7 @@
         <v>38.452321981424234</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -14621,7 +14626,7 @@
         <v>37.947781217750389</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -14631,12 +14636,12 @@
         <v>37.443240454076545</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="15">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="15">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
@@ -14644,7 +14649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>1896</v>
       </c>
@@ -14652,7 +14657,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <f>A31+1</f>
         <v>1897</v>
@@ -14661,14 +14666,14 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f t="shared" ref="A33:A48" si="4">A32+1</f>
         <v>1898</v>
       </c>
       <c r="B33" s="5"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" si="4"/>
         <v>1899</v>
@@ -14677,7 +14682,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f t="shared" si="4"/>
         <v>1900</v>
@@ -14686,7 +14691,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f t="shared" si="4"/>
         <v>1901</v>
@@ -14695,7 +14700,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="4"/>
         <v>1902</v>
@@ -14704,7 +14709,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f t="shared" si="4"/>
         <v>1903</v>
@@ -14713,7 +14718,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f t="shared" si="4"/>
         <v>1904</v>
@@ -14722,14 +14727,14 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f t="shared" si="4"/>
         <v>1905</v>
       </c>
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="4"/>
         <v>1906</v>
@@ -14738,7 +14743,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="4"/>
         <v>1907</v>
@@ -14747,28 +14752,28 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f t="shared" si="4"/>
         <v>1908</v>
       </c>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" si="4"/>
         <v>1909</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f t="shared" si="4"/>
         <v>1910</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f t="shared" si="4"/>
         <v>1911</v>
@@ -14777,7 +14782,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f t="shared" si="4"/>
         <v>1912</v>
@@ -14786,7 +14791,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f t="shared" si="4"/>
         <v>1913</v>
@@ -14805,21 +14810,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BD742E-198F-46A1-9FD2-0E0F39E4257B}">
   <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="20" max="20" width="22.625" customWidth="1"/>
-    <col min="21" max="21" width="21.25" customWidth="1"/>
-    <col min="22" max="22" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="20" max="20" width="22.5703125" customWidth="1"/>
+    <col min="21" max="21" width="21.28515625" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -14845,7 +14850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -14864,7 +14869,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -14892,7 +14897,7 @@
         <v>0.91381702647186103</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -14916,7 +14921,7 @@
         <v>1.8276340529437363</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -14940,7 +14945,7 @@
         <v>2.7414510794156115</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -14964,7 +14969,7 @@
         <v>3.6552681058874867</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -14988,7 +14993,7 @@
         <v>4.5690851323593478</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -15012,7 +15017,7 @@
         <v>5.4829021588312088</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -15036,7 +15041,7 @@
         <v>6.396719185303084</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -15060,7 +15065,7 @@
         <v>7.3105362117749593</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -15084,7 +15089,7 @@
         <v>8.2243532382468203</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -15108,7 +15113,7 @@
         <v>9.1381702647186813</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -15132,7 +15137,7 @@
         <v>10.051987291190571</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -15156,7 +15161,7 @@
         <v>10.965804317662446</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -15180,7 +15185,7 @@
         <v>11.879621344134307</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -15204,7 +15209,7 @@
         <v>12.793438370606168</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -15228,7 +15233,7 @@
         <v>13.707255397078043</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -15252,7 +15257,7 @@
         <v>14.621072423549919</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -15276,7 +15281,7 @@
         <v>15.534889450021538</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -15287,7 +15292,7 @@
         <v>39.667320261437908</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -15297,7 +15302,7 @@
         <v>39.233470932232535</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -15307,7 +15312,7 @@
         <v>38.799621603027163</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -15317,12 +15322,12 @@
         <v>38.36577227382179</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="15">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="15">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -15330,7 +15335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>1896</v>
       </c>
@@ -15338,7 +15343,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f>A32+1</f>
         <v>1897</v>
@@ -15347,14 +15352,14 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" ref="A34:A49" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f t="shared" si="5"/>
         <v>1899</v>
@@ -15363,7 +15368,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f t="shared" si="5"/>
         <v>1900</v>
@@ -15372,7 +15377,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="5"/>
         <v>1901</v>
@@ -15381,7 +15386,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f t="shared" si="5"/>
         <v>1902</v>
@@ -15390,7 +15395,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f t="shared" si="5"/>
         <v>1903</v>
@@ -15399,7 +15404,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f t="shared" si="5"/>
         <v>1904</v>
@@ -15408,14 +15413,14 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="5"/>
         <v>1905</v>
       </c>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="5"/>
         <v>1906</v>
@@ -15424,7 +15429,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f t="shared" si="5"/>
         <v>1907</v>
@@ -15433,28 +15438,28 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" si="5"/>
         <v>1908</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f t="shared" si="5"/>
         <v>1909</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f t="shared" si="5"/>
         <v>1910</v>
       </c>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f t="shared" si="5"/>
         <v>1911</v>
@@ -15463,7 +15468,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f t="shared" si="5"/>
         <v>1912</v>
@@ -15472,7 +15477,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <f t="shared" si="5"/>
         <v>1913</v>
@@ -15490,21 +15495,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D442F504-F5DF-44D0-8AAF-FB92847F2F5A}">
   <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="20" max="20" width="22.625" customWidth="1"/>
-    <col min="21" max="21" width="21.25" customWidth="1"/>
-    <col min="22" max="22" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="20" max="20" width="22.5703125" customWidth="1"/>
+    <col min="21" max="21" width="21.28515625" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -15530,7 +15535,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -15549,7 +15554,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -15577,7 +15582,7 @@
         <v>0.96695595203840412</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -15601,7 +15606,7 @@
         <v>1.933911904076794</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -15625,7 +15630,7 @@
         <v>2.9008678561151839</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -15649,7 +15654,7 @@
         <v>3.8678238081535739</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -15673,7 +15678,7 @@
         <v>4.834779760191978</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -15697,7 +15702,7 @@
         <v>5.8017357122303679</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -15721,7 +15726,7 @@
         <v>6.7686916642687578</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -15745,7 +15750,7 @@
         <v>7.7356476163069203</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -15769,7 +15774,7 @@
         <v>8.7026035683453102</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -15793,7 +15798,7 @@
         <v>9.6695595203837001</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -15817,7 +15822,7 @@
         <v>10.63651547242209</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -15841,7 +15846,7 @@
         <v>11.60347142446048</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -15865,7 +15870,7 @@
         <v>12.57042737649887</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -15889,7 +15894,7 @@
         <v>13.537383328537274</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -15913,7 +15918,7 @@
         <v>14.504339280575664</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -15937,7 +15942,7 @@
         <v>15.471295232614054</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -15961,7 +15966,7 @@
         <v>16.438251184652458</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f>A21+1</f>
         <v>1914</v>
@@ -15972,7 +15977,7 @@
         <v>37.816339869281023</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f>A22+1</f>
         <v>1915</v>
@@ -15982,7 +15987,7 @@
         <v>37.373615411076685</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f>A23+1</f>
         <v>1916</v>
@@ -15992,7 +15997,7 @@
         <v>36.930890952872346</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f>A24+1</f>
         <v>1917</v>
@@ -16002,12 +16007,12 @@
         <v>36.488166494668008</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="15">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="15">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -16015,7 +16020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>1896</v>
       </c>
@@ -16023,7 +16028,7 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f>A32+1</f>
         <v>1897</v>
@@ -16032,14 +16037,14 @@
         <v>45.1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" ref="A34:A49" si="5">A33+1</f>
         <v>1898</v>
       </c>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f t="shared" si="5"/>
         <v>1899</v>
@@ -16048,7 +16053,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f t="shared" si="5"/>
         <v>1900</v>
@@ -16057,7 +16062,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="5"/>
         <v>1901</v>
@@ -16066,7 +16071,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f t="shared" si="5"/>
         <v>1902</v>
@@ -16075,7 +16080,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f t="shared" si="5"/>
         <v>1903</v>
@@ -16084,7 +16089,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f t="shared" si="5"/>
         <v>1904</v>
@@ -16093,14 +16098,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="5"/>
         <v>1905</v>
       </c>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="5"/>
         <v>1906</v>
@@ -16109,7 +16114,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f t="shared" si="5"/>
         <v>1907</v>
@@ -16118,28 +16123,28 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" si="5"/>
         <v>1908</v>
       </c>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f t="shared" si="5"/>
         <v>1909</v>
       </c>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f t="shared" si="5"/>
         <v>1910</v>
       </c>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f t="shared" si="5"/>
         <v>1911</v>
@@ -16148,7 +16153,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f t="shared" si="5"/>
         <v>1912</v>
@@ -16157,7 +16162,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <f t="shared" si="5"/>
         <v>1913</v>
@@ -16175,18 +16180,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03EEFA1-9E72-4B80-AF4D-F111553A5002}">
   <dimension ref="A2:F22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="15" customHeight="1"/>
-    <row r="3" spans="1:6" ht="47.25" customHeight="1">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -16206,7 +16211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1896</v>
       </c>
@@ -16231,7 +16236,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+1</f>
         <v>1897</v>
@@ -16257,7 +16262,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A21" si="0">A5+1</f>
         <v>1898</v>
@@ -16283,7 +16288,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -16309,7 +16314,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -16335,7 +16340,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -16361,7 +16366,7 @@
         <v>43.7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -16387,7 +16392,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -16413,7 +16418,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -16439,7 +16444,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -16465,7 +16470,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -16491,7 +16496,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -16517,7 +16522,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -16543,7 +16548,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -16569,7 +16574,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -16595,7 +16600,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -16621,7 +16626,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -16647,7 +16652,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -16673,7 +16678,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>1914</v>
       </c>
